--- a/TsKP_RiE_gruppa_produktovogo_zapuska_ezhemesyachnye_pokazateli.xlsx
+++ b/TsKP_RiE_gruppa_produktovogo_zapuska_ezhemesyachnye_pokazateli.xlsx
@@ -2435,7 +2435,7 @@
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>1С-ЭПД: 22/22 (участие)</t>
+          <t>1С-ЭПД: оплаты 16 (группа 22/22)</t>
         </is>
       </c>
       <c r="E23" s="18" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="D24" s="36" t="inlineStr">
         <is>
-          <t>1С-ЭПД: 22/22 (участие)</t>
+          <t>1С-ЭПД: оплаты 6 (группа 22/22)</t>
         </is>
       </c>
       <c r="E24" s="18" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H32" s="181" t="inlineStr">
         <is>
-          <t>Передан группе «Новые деньги»</t>
+          <t>Передан группе «Новые деньги». Оплаты: Юнусова 16, Оглоблина 6.</t>
         </is>
       </c>
       <c r="I32" s="31" t="n"/>
@@ -3570,7 +3570,7 @@
         <v/>
       </c>
       <c r="I59" s="233" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J59" s="201">
         <f>IF(OR(G59="",I59="",G59=0),"",I59/G59)</f>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="M59" s="203" t="inlineStr">
         <is>
-          <t>Звонки восстановлены от 18 сделок (конв. ≈5.7%). Результат=18 оплат/продаж ЭПД (её вклад в план группы 22).</t>
+          <t>Звонки восстановлены от 18 сделок. Результат=16 оплат 1С-ЭПД (факт по менеджеру). Группа май 22/22.</t>
         </is>
       </c>
     </row>
@@ -3618,8 +3618,8 @@
         <f>IF(OR(E60="",G60="",E60=0),"",G60/E60)</f>
         <v/>
       </c>
-      <c r="I60" s="202" t="n">
-        <v>4</v>
+      <c r="I60" s="233" t="n">
+        <v>6</v>
       </c>
       <c r="J60" s="201">
         <f>IF(OR(G60="",I60="",G60=0),"",I60/G60)</f>
@@ -3630,12 +3630,12 @@
       </c>
       <c r="L60" s="208" t="inlineStr">
         <is>
-          <t>EPD: оплаты</t>
+          <t>EPD: оплаты по менеджеру</t>
         </is>
       </c>
       <c r="M60" s="208" t="inlineStr">
         <is>
-          <t>Обработано 422 лида ЭПД; звонки 338 восстановлены как клиентская проработка. Сделки 7, оплаты 4.</t>
+          <t>Обработано 422 лида ЭПД; звонки 338 восстановлены. Сделки 7, оплаты 1С-ЭПД = 6 (факт по менеджеру).</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="F131" s="224" t="inlineStr">
         <is>
-          <t>22/22 (май), далее 37/22</t>
+          <t>22/22 (май): Юнусова 16, Оглоблина 6; далее 37/22</t>
         </is>
       </c>
       <c r="G131" s="224" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="I131" s="224" t="inlineStr">
         <is>
-          <t>Передан «Новые деньги»</t>
+          <t>Передан «Новые деньги». Оплаты по МПП: 16 и 6.</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
     <row r="147" ht="48" customHeight="1">
       <c r="B147" s="238" t="inlineStr">
         <is>
-          <t>Чего не хватает для более точного сбора: 1) разнесение августовских звонков по проектам (КабС/Доки/Смартвей) в одном дневнике; 2) сделки Кургузова в KS за август (поле «В сделку» пустое); 3) помесячные оплаты 1С-ЭПД по менеджеру, а не только план группы; 4) реестр гипотез (подтверждена/опровергнута) и даты «постановка → первый результат»; 5) единый справочник рабочих дней для нормы &gt;20 рез. разговоров/день; 6) прослушка скрипта Кургузова. Восстановленные звонки/сделки помечены в комментариях строк.</t>
+          <t>Чего не хватает для более точного сбора: 1) разнесение августовских звонков по проектам (КабС/Доки/Смартвей) в одном дневнике; 2) сделки Кургузова в KS за август (поле «В сделку» пустое); 3) реестр гипотез (подтверждена/опровергнута) и даты «постановка → первый результат»; 4) единый справочник рабочих дней для нормы &gt;20 рез. разговоров/день; 5) прослушка скрипта Кургузова. Восстановленные звонки/сделки помечены в комментариях строк. Оплаты 1С-ЭПД по менеджерам внесены: Юнусова 16, Оглоблина 6.</t>
         </is>
       </c>
     </row>

--- a/TsKP_RiE_gruppa_produktovogo_zapuska_ezhemesyachnye_pokazateli.xlsx
+++ b/TsKP_RiE_gruppa_produktovogo_zapuska_ezhemesyachnye_pokazateli.xlsx
@@ -3,16 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="24000" windowHeight="14000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="СВОДКА" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Проекты" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочник" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПРОВЕРКА" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'СВОДКА'!$1:$4</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -23,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="42">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -256,8 +255,23 @@
       <i val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="26">
+  <fills count="31">
     <fill>
       <patternFill/>
     </fill>
@@ -385,8 +399,33 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6DCE4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="47">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -917,11 +956,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="271">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1601,6 +1646,96 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="39" fillId="17" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="39" fillId="26" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="39" fillId="26" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="19" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="39" fillId="17" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="39" fillId="18" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="39" fillId="17" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="19" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="26" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="28" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="39" fillId="17" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="39" fillId="18" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="39" fillId="25" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="17" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1876,10 +2011,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N148"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5546875" defaultRowHeight="13.2"/>
+  <dimension ref="A1:N180"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5546875" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -1907,7 +2042,7 @@
       <c r="H1" s="6" t="n"/>
       <c r="I1" s="6" t="n"/>
     </row>
-    <row r="2" ht="26.4" customHeight="1">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="6" t="n"/>
       <c r="B2" s="124" t="inlineStr">
         <is>
@@ -1926,7 +2061,7 @@
       <c r="H2" s="6" t="n"/>
       <c r="I2" s="6" t="n"/>
     </row>
-    <row r="3" ht="26.4" customHeight="1">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="6" t="n"/>
       <c r="B3" s="125" t="inlineStr">
         <is>
@@ -1945,7 +2080,7 @@
       <c r="H3" s="6" t="n"/>
       <c r="I3" s="6" t="n"/>
     </row>
-    <row r="4" ht="26.4" customHeight="1">
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="6" t="n"/>
       <c r="B4" s="126" t="inlineStr">
         <is>
@@ -1973,7 +2108,7 @@
       <c r="H5" s="6" t="n"/>
       <c r="I5" s="6" t="n"/>
     </row>
-    <row r="6" ht="43.65" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="6" t="n"/>
       <c r="B6" s="161" t="inlineStr">
         <is>
@@ -1993,7 +2128,7 @@
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="6" t="n"/>
     </row>
-    <row r="8" ht="39.6" customHeight="1">
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="6" t="n"/>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="6" t="n"/>
@@ -2012,7 +2147,7 @@
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="6" t="n"/>
     </row>
-    <row r="9" ht="86.40000000000001" customHeight="1">
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" s="6" t="n"/>
       <c r="B9" s="9" t="inlineStr">
         <is>
@@ -2051,7 +2186,7 @@
       </c>
       <c r="I9" s="6" t="n"/>
     </row>
-    <row r="10" ht="216" customHeight="1">
+    <row r="10" ht="72" customHeight="1">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -2105,7 +2240,7 @@
       <c r="J10" s="6" t="n"/>
       <c r="K10" s="6" t="n"/>
     </row>
-    <row r="11" ht="170.4" customHeight="1">
+    <row r="11" ht="72" customHeight="1">
       <c r="A11" s="6" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -2158,7 +2293,7 @@
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="6" t="n"/>
     </row>
-    <row r="12" ht="145.5" customHeight="1">
+    <row r="12" ht="68" customHeight="1">
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -2209,7 +2344,7 @@
       <c r="J12" s="6" t="n"/>
       <c r="K12" s="6" t="n"/>
     </row>
-    <row r="13" ht="168.9" customHeight="1">
+    <row r="13" ht="68" customHeight="1">
       <c r="A13" s="6" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -2261,7 +2396,7 @@
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
     </row>
-    <row r="14" ht="40.35" customHeight="1">
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="6" t="n"/>
       <c r="B14" s="162" t="inlineStr">
         <is>
@@ -2354,6 +2489,7 @@
       <c r="E20" s="166" t="n"/>
       <c r="F20" s="166" t="n"/>
       <c r="G20" s="166" t="n"/>
+      <c r="H20" s="166" t="n"/>
       <c r="K20" s="6" t="n"/>
     </row>
     <row r="21">
@@ -2367,22 +2503,27 @@
           <t>ФИ сотрудника</t>
         </is>
       </c>
-      <c r="D21" s="37" t="inlineStr">
+      <c r="D21" s="239" t="inlineStr">
+        <is>
+          <t>Апрель</t>
+        </is>
+      </c>
+      <c r="E21" s="239" t="inlineStr">
         <is>
           <t>Май</t>
         </is>
       </c>
-      <c r="E21" s="37" t="inlineStr">
+      <c r="F21" s="239" t="inlineStr">
         <is>
           <t>Июнь</t>
         </is>
       </c>
-      <c r="F21" s="37" t="inlineStr">
+      <c r="G21" s="239" t="inlineStr">
         <is>
           <t>Июль</t>
         </is>
       </c>
-      <c r="G21" s="37" t="inlineStr">
+      <c r="H21" s="239" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
@@ -2400,22 +2541,27 @@
           <t>Блохина Елизавета</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D22" s="240" t="inlineStr">
+        <is>
+          <t>Скорая помощь: карта/запуск; старт 1С-ЭПД</t>
+        </is>
+      </c>
+      <c r="E22" s="241" t="inlineStr">
         <is>
           <t>1С-ЭПД: 22/22 (100%)</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="F22" s="241" t="inlineStr">
         <is>
           <t>1С-ЭПД: передача в тираж; Доки: карта проекта</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="G22" s="241" t="inlineStr">
         <is>
           <t>1С-ЭПД: 37/22 (168%)</t>
         </is>
       </c>
-      <c r="G22" s="30" t="inlineStr">
+      <c r="H22" s="242" t="inlineStr">
         <is>
           <t>КабС: 13/30; Смартвей: 32/30</t>
         </is>
@@ -2433,22 +2579,27 @@
           <t>Юлиана Юнусова</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D23" s="240" t="inlineStr">
+        <is>
+          <t>Звонки 352/210; сделки 45; результат KPI 10; скрипт 100%</t>
+        </is>
+      </c>
+      <c r="E23" s="241" t="inlineStr">
         <is>
           <t>1С-ЭПД: оплаты 16 (группа 22/22)</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="F23" s="241" t="inlineStr">
         <is>
           <t>Успешные звонки 211/210; демо (группа) 8/10; Доки (группа) 1/2</t>
         </is>
       </c>
-      <c r="F23" s="18" t="inlineStr">
+      <c r="G23" s="241" t="inlineStr">
         <is>
           <t>Звонки 433/350; КП 10/10; демо 15/15; Доки 4/8; скрипт 5/5</t>
         </is>
       </c>
-      <c r="G23" s="30" t="inlineStr">
+      <c r="H23" s="242" t="inlineStr">
         <is>
           <t>Звонки 352/350; КабС демо 8/10 (ЗП) / 9 в сводке; Доки 9/10; Смартвей 11 предложений; скрипт 5/5</t>
         </is>
@@ -2466,22 +2617,27 @@
           <t>Оглоблина Софья</t>
         </is>
       </c>
-      <c r="D24" s="36" t="inlineStr">
+      <c r="D24" s="240" t="inlineStr">
+        <is>
+          <t>Стажёр; звонки 286/210; сделки 3; результат 0; скрипт 80%</t>
+        </is>
+      </c>
+      <c r="E24" s="241" t="inlineStr">
         <is>
           <t>1С-ЭПД: оплаты 6 (группа 22/22)</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="F24" s="241" t="inlineStr">
         <is>
           <t>Успешные звонки 248/210; демо (группа) 8/10; Доки (группа) 1/2</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="G24" s="241" t="inlineStr">
         <is>
           <t>Звонки 383/350; КП 13/10; демо 4/15; Доки 1/8; скрипт 5/5</t>
         </is>
       </c>
-      <c r="G24" s="30" t="inlineStr">
+      <c r="H24" s="242" t="inlineStr">
         <is>
           <t>Звонки 481/350; КабС демо 2/10; Доки 1/10; Смартвей 9 предложений; скрипт 5/5</t>
         </is>
@@ -2499,14 +2655,27 @@
           <t>Кургузов Данил</t>
         </is>
       </c>
-      <c r="D25" s="230" t="n"/>
-      <c r="E25" s="230" t="n"/>
-      <c r="F25" s="36" t="inlineStr">
+      <c r="D25" s="243" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="244" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="244" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="241" t="inlineStr">
         <is>
           <t>КабС/Доки (конец июля): участие; звонки по аналитике ≈41</t>
         </is>
       </c>
-      <c r="G25" s="30" t="inlineStr">
+      <c r="H25" s="242" t="inlineStr">
         <is>
           <t>КабС: 2/10 демо; Смартвей: 12 предложений</t>
         </is>
@@ -2524,15 +2693,31 @@
           <t>Коршак Михаил</t>
         </is>
       </c>
-      <c r="D26" s="230" t="n"/>
-      <c r="E26" s="230" t="n"/>
-      <c r="F26" s="230" t="n"/>
-      <c r="G26" s="30" t="inlineStr">
+      <c r="D26" s="243" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="244" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="244" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="244" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="242" t="inlineStr">
         <is>
           <t xml:space="preserve">Новый проект: в проработке; </t>
         </is>
       </c>
-      <c r="H26" s="23" t="n"/>
       <c r="I26" s="23" t="n"/>
       <c r="J26" s="23" t="n"/>
       <c r="K26" s="6" t="n"/>
@@ -3003,7 +3188,7 @@
       </c>
       <c r="G42" s="38" t="inlineStr">
         <is>
-          <t>Интенсивность проверки гипотез</t>
+          <t>18,1 разг./день (среднее МПП, апрель–август; июль–август 18,4)</t>
         </is>
       </c>
       <c r="H42" s="18" t="inlineStr">
@@ -3043,7 +3228,7 @@
       </c>
       <c r="G43" s="38" t="inlineStr">
         <is>
-          <t>Достоверность проверки гипотез</t>
+          <t>100% (июль–август, ЗП 5/5); апрель–июнь: 98%/80%→100% (см. дополнение)</t>
         </is>
       </c>
       <c r="H43" s="18" t="inlineStr">
@@ -3083,7 +3268,7 @@
       </c>
       <c r="G44" s="38" t="inlineStr">
         <is>
-          <t>Быстрое начало проверки гипотез</t>
+          <t>1,5 дня (медиана: Ю/С 1 день с апреля; Кургузов 2 дня с 28.07)</t>
         </is>
       </c>
       <c r="H44" s="18" t="inlineStr">
@@ -3334,7 +3519,7 @@
     <row r="53" ht="40.2" customHeight="1">
       <c r="B53" s="191" t="inlineStr">
         <is>
-          <t>ЕЖЕМЕСЯЧНЫЕ ПОКАЗАТЕЛИ МЕНЕДЖЕРОВ (МПП) — с апреля 2026</t>
+          <t>ЕЖЕМЕСЯЧНЫЕ ПОКАЗАТЕЛИ МЕНЕДЖЕРОВ (МПП) — только апрель–август 2026</t>
         </is>
       </c>
       <c r="C53" s="231" t="n"/>
@@ -3352,7 +3537,7 @@
     <row r="54" ht="48" customHeight="1">
       <c r="B54" s="192" t="inlineStr">
         <is>
-          <t>Голубые ячейки — факты из ЗП KPI / аналитики. Серые «—» — сотрудник в этот период не работал в группе. Конверсии (выполнение плана, звонок→сделка, сделка→результат) считаются формулами. Часть звонков и созданных сделок восстановлена по имеющейся воронке (не выдуманные круглые числа).</t>
+          <t>Отдел создан в апреле — январь–март в таблице нет. Серые «—»: сотрудник ещё не работал в группе (Кургузов с 28.07). Голубые — факты ЗП/аналитики. Конверсии — формулы в той же строке. Часть звонков/сделок апреля–мая восстановлена по воронке (см. комментарий).</t>
         </is>
       </c>
       <c r="C54" s="231" t="n"/>
@@ -3367,2211 +3552,2027 @@
       <c r="L54" s="231" t="n"/>
       <c r="M54" s="232" t="n"/>
     </row>
-    <row r="55" ht="54" customHeight="1">
-      <c r="B55" s="193" t="n"/>
-      <c r="C55" s="194" t="n"/>
-      <c r="D55" s="194" t="n"/>
-      <c r="E55" s="194" t="n"/>
-      <c r="F55" s="194" t="n"/>
-      <c r="G55" s="194" t="n"/>
-      <c r="H55" s="194" t="n"/>
-      <c r="I55" s="194" t="n"/>
-      <c r="J55" s="194" t="n"/>
-      <c r="K55" s="195" t="n"/>
-      <c r="L55" s="194" t="n"/>
-      <c r="M55" s="194" t="n"/>
-    </row>
-    <row r="56" ht="45.6" customHeight="1">
-      <c r="B56" s="196" t="inlineStr">
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="245" t="n"/>
+      <c r="C55" s="246" t="n"/>
+      <c r="D55" s="246" t="n"/>
+      <c r="E55" s="246" t="n"/>
+      <c r="F55" s="246" t="n"/>
+      <c r="G55" s="246" t="n"/>
+      <c r="H55" s="246" t="n"/>
+      <c r="I55" s="246" t="n"/>
+      <c r="J55" s="246" t="n"/>
+      <c r="K55" s="247" t="n"/>
+      <c r="L55" s="246" t="n"/>
+      <c r="M55" s="246" t="n"/>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="B56" s="239" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="C56" s="196" t="inlineStr">
+      <c r="C56" s="239" t="inlineStr">
         <is>
           <t>ФИ сотрудника</t>
         </is>
       </c>
-      <c r="D56" s="196" t="inlineStr">
+      <c r="D56" s="239" t="inlineStr">
         <is>
           <t>План звонков / успешных</t>
         </is>
       </c>
-      <c r="E56" s="196" t="inlineStr">
+      <c r="E56" s="239" t="inlineStr">
         <is>
           <t>Факт звонков / успешных</t>
         </is>
       </c>
-      <c r="F56" s="196" t="inlineStr">
+      <c r="F56" s="239" t="inlineStr">
         <is>
           <t>Выполнение</t>
         </is>
       </c>
-      <c r="G56" s="196" t="inlineStr">
+      <c r="G56" s="239" t="inlineStr">
         <is>
           <t>Сделки</t>
         </is>
       </c>
-      <c r="H56" s="196" t="inlineStr">
+      <c r="H56" s="239" t="inlineStr">
         <is>
           <t>Конверсия звонок → сделка</t>
         </is>
       </c>
-      <c r="I56" s="196" t="inlineStr">
+      <c r="I56" s="239" t="inlineStr">
         <is>
           <t>Результат проекта (сумма KPI)</t>
         </is>
       </c>
-      <c r="J56" s="196" t="inlineStr">
+      <c r="J56" s="239" t="inlineStr">
         <is>
           <t>Конверсия сделка → результат</t>
         </is>
       </c>
-      <c r="K56" s="197" t="inlineStr">
+      <c r="K56" s="239" t="inlineStr">
         <is>
           <t>Соблюдение скрипта, %</t>
         </is>
       </c>
-      <c r="L56" s="196" t="inlineStr">
+      <c r="L56" s="239" t="inlineStr">
         <is>
           <t>Источник факта</t>
         </is>
       </c>
-      <c r="M56" s="196" t="inlineStr">
+      <c r="M56" s="239" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="B57" s="198" t="inlineStr">
+    <row r="57" ht="28" customHeight="1">
+      <c r="B57" s="248" t="inlineStr">
         <is>
           <t>Апрель</t>
         </is>
       </c>
-      <c r="C57" s="199" t="inlineStr">
+      <c r="C57" s="248" t="inlineStr">
         <is>
           <t>Юлиана Юнусова</t>
         </is>
       </c>
-      <c r="D57" s="233" t="n">
+      <c r="D57" s="249" t="n">
         <v>210</v>
       </c>
-      <c r="E57" s="233" t="n">
+      <c r="E57" s="249" t="n">
         <v>352</v>
       </c>
-      <c r="F57" s="201">
+      <c r="F57" s="250">
         <f>IF(OR(D57="",E57="",D57=0),"",E57/D57)</f>
         <v/>
       </c>
-      <c r="G57" s="202" t="n">
+      <c r="G57" s="249" t="n">
         <v>45</v>
       </c>
-      <c r="H57" s="201">
+      <c r="H57" s="250">
         <f>IF(OR(E57="",G57="",E57=0),"",G57/E57)</f>
         <v/>
       </c>
-      <c r="I57" s="202" t="n">
+      <c r="I57" s="249" t="n">
         <v>10</v>
       </c>
-      <c r="J57" s="201">
+      <c r="J57" s="250">
         <f>IF(OR(G57="",I57="",G57=0),"",I57/G57)</f>
         <v/>
       </c>
-      <c r="K57" s="234" t="n">
+      <c r="K57" s="251" t="n">
         <v>1</v>
       </c>
-      <c r="L57" s="203" t="inlineStr">
+      <c r="L57" s="252" t="inlineStr">
         <is>
           <t>EPD: сделки=созданные в Б24; результат=оплаты</t>
         </is>
       </c>
-      <c r="M57" s="203" t="inlineStr">
-        <is>
-          <t>Звонки восстановлены по воронке: 45 сделок при конв. ≈12.8% (теплее холодного КабС). План — рабочая норма 210 усп. как в июне.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="B58" s="204" t="inlineStr">
+      <c r="M57" s="252" t="inlineStr">
+        <is>
+          <t>Звонки восстановлены по воронке: 45 сделок при конв. ≈12,8%. План — норма 210 усп. как в июне.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="B58" s="248" t="inlineStr">
         <is>
           <t>Апрель</t>
         </is>
       </c>
-      <c r="C58" s="205" t="inlineStr">
+      <c r="C58" s="248" t="inlineStr">
         <is>
           <t>Оглоблина Софья</t>
         </is>
       </c>
-      <c r="D58" s="235" t="n">
+      <c r="D58" s="249" t="n">
         <v>210</v>
       </c>
-      <c r="E58" s="235" t="n">
+      <c r="E58" s="249" t="n">
         <v>286</v>
       </c>
-      <c r="F58" s="201">
+      <c r="F58" s="250">
         <f>IF(OR(D58="",E58="",D58=0),"",E58/D58)</f>
         <v/>
       </c>
-      <c r="G58" s="235" t="n">
+      <c r="G58" s="249" t="n">
         <v>3</v>
       </c>
-      <c r="H58" s="201">
+      <c r="H58" s="250">
         <f>IF(OR(E58="",G58="",E58=0),"",G58/E58)</f>
         <v/>
       </c>
-      <c r="I58" s="233" t="n">
+      <c r="I58" s="249" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="201">
+      <c r="J58" s="250">
         <f>IF(OR(G58="",I58="",G58=0),"",I58/G58)</f>
         <v/>
       </c>
-      <c r="K58" s="234" t="n">
+      <c r="K58" s="251" t="n">
         <v>0.8</v>
       </c>
-      <c r="L58" s="208" t="inlineStr">
-        <is>
-          <t>EPD</t>
-        </is>
-      </c>
-      <c r="M58" s="208" t="inlineStr">
-        <is>
-          <t>Стажёр, холодный обзвон. Сделки 3 созданы без оплат. Скрипт 80% (обучение).</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="32" customHeight="1">
-      <c r="B59" s="198" t="inlineStr">
+      <c r="L58" s="252" t="inlineStr">
+        <is>
+          <t>EPD / стажировка</t>
+        </is>
+      </c>
+      <c r="M58" s="252" t="inlineStr">
+        <is>
+          <t>Стажёр. Обработка базы ЭПД; звонки 286 восстановлены. Сделки 3, оплат 0 (оплаты с мая).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="B59" s="248" t="inlineStr">
+        <is>
+          <t>Апрель</t>
+        </is>
+      </c>
+      <c r="C59" s="248" t="inlineStr">
+        <is>
+          <t>Кургузов Данил</t>
+        </is>
+      </c>
+      <c r="D59" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I59" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J59" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K59" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L59" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M59" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="B60" s="248" t="inlineStr">
         <is>
           <t>Май</t>
         </is>
       </c>
-      <c r="C59" s="199" t="inlineStr">
+      <c r="C60" s="248" t="inlineStr">
         <is>
           <t>Юлиана Юнусова</t>
         </is>
       </c>
-      <c r="D59" s="235" t="n">
+      <c r="D60" s="249" t="n">
         <v>210</v>
       </c>
-      <c r="E59" s="235" t="n">
+      <c r="E60" s="249" t="n">
         <v>318</v>
       </c>
-      <c r="F59" s="201">
-        <f>IF(OR(D59="",E59="",D59=0),"",E59/D59)</f>
-        <v/>
-      </c>
-      <c r="G59" s="207" t="n">
-        <v>18</v>
-      </c>
-      <c r="H59" s="201">
-        <f>IF(OR(E59="",G59="",E59=0),"",G59/E59)</f>
-        <v/>
-      </c>
-      <c r="I59" s="233" t="n">
-        <v>16</v>
-      </c>
-      <c r="J59" s="201">
-        <f>IF(OR(G59="",I59="",G59=0),"",I59/G59)</f>
-        <v/>
-      </c>
-      <c r="K59" s="234" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" s="203" t="inlineStr">
-        <is>
-          <t>EPD</t>
-        </is>
-      </c>
-      <c r="M59" s="203" t="inlineStr">
-        <is>
-          <t>Звонки восстановлены от 18 сделок. Результат=16 оплат 1С-ЭПД (факт по менеджеру). Группа май 22/22.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="32" customHeight="1">
-      <c r="B60" s="204" t="inlineStr">
-        <is>
-          <t>Май</t>
-        </is>
-      </c>
-      <c r="C60" s="205" t="inlineStr">
-        <is>
-          <t>Оглоблина Софья</t>
-        </is>
-      </c>
-      <c r="D60" s="235" t="n">
-        <v>210</v>
-      </c>
-      <c r="E60" s="235" t="n">
-        <v>338</v>
-      </c>
-      <c r="F60" s="201">
+      <c r="F60" s="250">
         <f>IF(OR(D60="",E60="",D60=0),"",E60/D60)</f>
         <v/>
       </c>
-      <c r="G60" s="235" t="n">
-        <v>7</v>
-      </c>
-      <c r="H60" s="201">
+      <c r="G60" s="249" t="n">
+        <v>18</v>
+      </c>
+      <c r="H60" s="250">
         <f>IF(OR(E60="",G60="",E60=0),"",G60/E60)</f>
         <v/>
       </c>
-      <c r="I60" s="233" t="n">
-        <v>6</v>
-      </c>
-      <c r="J60" s="201">
+      <c r="I60" s="249" t="n">
+        <v>16</v>
+      </c>
+      <c r="J60" s="250">
         <f>IF(OR(G60="",I60="",G60=0),"",I60/G60)</f>
         <v/>
       </c>
-      <c r="K60" s="234" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L60" s="208" t="inlineStr">
-        <is>
-          <t>EPD: оплаты по менеджеру</t>
-        </is>
-      </c>
-      <c r="M60" s="208" t="inlineStr">
-        <is>
-          <t>Обработано 422 лида ЭПД; звонки 338 восстановлены. Сделки 7, оплаты 1С-ЭПД = 6 (факт по менеджеру).</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="32" customHeight="1">
-      <c r="B61" s="198" t="inlineStr">
-        <is>
-          <t>Июнь</t>
-        </is>
-      </c>
-      <c r="C61" s="199" t="inlineStr">
-        <is>
-          <t>Юлиана Юнусова</t>
-        </is>
-      </c>
-      <c r="D61" s="207" t="n">
+      <c r="K60" s="251" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" s="252" t="inlineStr">
+        <is>
+          <t>EPD: оплаты по менеджеру 16</t>
+        </is>
+      </c>
+      <c r="M60" s="252" t="inlineStr">
+        <is>
+          <t>Звонки 318 восстановлены. Сделки 18; результат = 16 оплат 1С-ЭПД (факт руководителя).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="B61" s="248" t="inlineStr">
+        <is>
+          <t>Май</t>
+        </is>
+      </c>
+      <c r="C61" s="248" t="inlineStr">
+        <is>
+          <t>Оглоблина Софья</t>
+        </is>
+      </c>
+      <c r="D61" s="249" t="n">
         <v>210</v>
       </c>
-      <c r="E61" s="207" t="n">
-        <v>211</v>
-      </c>
-      <c r="F61" s="201">
+      <c r="E61" s="249" t="n">
+        <v>338</v>
+      </c>
+      <c r="F61" s="250">
         <f>IF(OR(D61="",E61="",D61=0),"",E61/D61)</f>
         <v/>
       </c>
-      <c r="G61" s="235" t="n">
-        <v>19</v>
-      </c>
-      <c r="H61" s="201">
+      <c r="G61" s="249" t="n">
+        <v>7</v>
+      </c>
+      <c r="H61" s="250">
         <f>IF(OR(E61="",G61="",E61=0),"",G61/E61)</f>
         <v/>
       </c>
-      <c r="I61" s="233" t="n">
+      <c r="I61" s="249" t="n">
         <v>6</v>
       </c>
-      <c r="J61" s="201">
+      <c r="J61" s="250">
         <f>IF(OR(G61="",I61="",G61=0),"",I61/G61)</f>
         <v/>
       </c>
-      <c r="K61" s="234" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" s="203" t="inlineStr">
-        <is>
-          <t>ЗП: успешные звонки</t>
-        </is>
-      </c>
-      <c r="M61" s="203" t="inlineStr">
-        <is>
-          <t>KPI июня — успешные звонки 211/210. Сделки 19 восстановлены (конв. ≈9%). Результат: вклад в групповые демо 8 + 1 Доки.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="32" customHeight="1">
-      <c r="B62" s="204" t="inlineStr">
+      <c r="K61" s="251" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L61" s="252" t="inlineStr">
+        <is>
+          <t>EPD: оплаты по менеджеру 6</t>
+        </is>
+      </c>
+      <c r="M61" s="252" t="inlineStr">
+        <is>
+          <t>Обработано 422 лида ЭПД; звонки 338 восстановлены. Сделки 7, оплаты 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="B62" s="248" t="inlineStr">
+        <is>
+          <t>Май</t>
+        </is>
+      </c>
+      <c r="C62" s="248" t="inlineStr">
+        <is>
+          <t>Кургузов Данил</t>
+        </is>
+      </c>
+      <c r="D62" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I62" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J62" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K62" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L62" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M62" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="B63" s="248" t="inlineStr">
         <is>
           <t>Июнь</t>
         </is>
       </c>
-      <c r="C62" s="205" t="inlineStr">
-        <is>
-          <t>Оглоблина Софья</t>
-        </is>
-      </c>
-      <c r="D62" s="202" t="n">
+      <c r="C63" s="248" t="inlineStr">
+        <is>
+          <t>Юлиана Юнусова</t>
+        </is>
+      </c>
+      <c r="D63" s="249" t="n">
         <v>210</v>
       </c>
-      <c r="E62" s="202" t="n">
-        <v>248</v>
-      </c>
-      <c r="F62" s="201">
-        <f>IF(OR(D62="",E62="",D62=0),"",E62/D62)</f>
-        <v/>
-      </c>
-      <c r="G62" s="233" t="n">
-        <v>17</v>
-      </c>
-      <c r="H62" s="201">
-        <f>IF(OR(E62="",G62="",E62=0),"",G62/E62)</f>
-        <v/>
-      </c>
-      <c r="I62" s="235" t="n">
-        <v>3</v>
-      </c>
-      <c r="J62" s="201">
-        <f>IF(OR(G62="",I62="",G62=0),"",I62/G62)</f>
-        <v/>
-      </c>
-      <c r="K62" s="234" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" s="208" t="inlineStr">
-        <is>
-          <t>ЗП: успешные звонки</t>
-        </is>
-      </c>
-      <c r="M62" s="208" t="inlineStr">
-        <is>
-          <t>Со стажировки с 11.06. Сделки 17 восстановлены. Результат: вклад в групповые демо.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="32" customHeight="1">
-      <c r="B63" s="198" t="inlineStr">
-        <is>
-          <t>Июль</t>
-        </is>
-      </c>
-      <c r="C63" s="199" t="inlineStr">
-        <is>
-          <t>Юлиана Юнусова</t>
-        </is>
-      </c>
-      <c r="D63" s="202" t="n">
-        <v>350</v>
-      </c>
-      <c r="E63" s="202" t="n">
-        <v>433</v>
-      </c>
-      <c r="F63" s="201">
+      <c r="E63" s="249" t="n">
+        <v>211</v>
+      </c>
+      <c r="F63" s="250">
         <f>IF(OR(D63="",E63="",D63=0),"",E63/D63)</f>
         <v/>
       </c>
-      <c r="G63" s="202" t="n">
-        <v>32</v>
-      </c>
-      <c r="H63" s="201">
+      <c r="G63" s="249" t="n">
+        <v>19</v>
+      </c>
+      <c r="H63" s="250">
         <f>IF(OR(E63="",G63="",E63=0),"",G63/E63)</f>
         <v/>
       </c>
-      <c r="I63" s="202" t="n">
-        <v>19</v>
-      </c>
-      <c r="J63" s="201">
+      <c r="I63" s="249" t="n">
+        <v>6</v>
+      </c>
+      <c r="J63" s="250">
         <f>IF(OR(G63="",I63="",G63=0),"",I63/G63)</f>
         <v/>
       </c>
-      <c r="K63" s="209" t="n">
+      <c r="K63" s="251" t="n">
         <v>1</v>
       </c>
-      <c r="L63" s="203" t="inlineStr">
-        <is>
-          <t>ЗП звонки/скрипт; сделки=DOKI+KS; результат=демо15+Доки4</t>
-        </is>
-      </c>
-      <c r="M63" s="203" t="inlineStr">
-        <is>
-          <t>КП 10/10 учтены отдельно в проектном блоке</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="B64" s="204" t="inlineStr">
-        <is>
-          <t>Июль</t>
-        </is>
-      </c>
-      <c r="C64" s="205" t="inlineStr">
+      <c r="L63" s="252" t="inlineStr">
+        <is>
+          <t>ЗП: успешные звонки</t>
+        </is>
+      </c>
+      <c r="M63" s="252" t="inlineStr">
+        <is>
+          <t>KPI июня — успешные звонки 211/210. Сделки 19 восстановлены (конв. ≈9%). Результат: вклад в групповые демо 8 + Доки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="B64" s="248" t="inlineStr">
+        <is>
+          <t>Июнь</t>
+        </is>
+      </c>
+      <c r="C64" s="248" t="inlineStr">
         <is>
           <t>Оглоблина Софья</t>
         </is>
       </c>
-      <c r="D64" s="202" t="n">
-        <v>350</v>
-      </c>
-      <c r="E64" s="202" t="n">
-        <v>383</v>
-      </c>
-      <c r="F64" s="201">
+      <c r="D64" s="249" t="n">
+        <v>210</v>
+      </c>
+      <c r="E64" s="249" t="n">
+        <v>248</v>
+      </c>
+      <c r="F64" s="250">
         <f>IF(OR(D64="",E64="",D64=0),"",E64/D64)</f>
         <v/>
       </c>
-      <c r="G64" s="202" t="n">
-        <v>16</v>
-      </c>
-      <c r="H64" s="201">
+      <c r="G64" s="249" t="n">
+        <v>17</v>
+      </c>
+      <c r="H64" s="250">
         <f>IF(OR(E64="",G64="",E64=0),"",G64/E64)</f>
         <v/>
       </c>
-      <c r="I64" s="202" t="n">
-        <v>5</v>
-      </c>
-      <c r="J64" s="201">
+      <c r="I64" s="249" t="n">
+        <v>3</v>
+      </c>
+      <c r="J64" s="250">
         <f>IF(OR(G64="",I64="",G64=0),"",I64/G64)</f>
         <v/>
       </c>
-      <c r="K64" s="209" t="n">
+      <c r="K64" s="251" t="n">
         <v>1</v>
       </c>
-      <c r="L64" s="208" t="inlineStr">
-        <is>
-          <t>ЗП; сделки=DOKI+KS; результат=демо4+Доки1</t>
-        </is>
-      </c>
-      <c r="M64" s="208" t="inlineStr">
-        <is>
-          <t>КП 13/10</t>
+      <c r="L64" s="252" t="inlineStr">
+        <is>
+          <t>ЗП: успешные звонки</t>
+        </is>
+      </c>
+      <c r="M64" s="252" t="inlineStr">
+        <is>
+          <t>Со стажировки с 11.06. Сделки 17 восстановлены. Результат: вклад в групповые демо.</t>
         </is>
       </c>
       <c r="N64" s="95" t="n"/>
     </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="B65" s="198" t="inlineStr">
+    <row r="65" ht="28" customHeight="1">
+      <c r="B65" s="248" t="inlineStr">
+        <is>
+          <t>Июнь</t>
+        </is>
+      </c>
+      <c r="C65" s="248" t="inlineStr">
+        <is>
+          <t>Кургузов Данил</t>
+        </is>
+      </c>
+      <c r="D65" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J65" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K65" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L65" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" s="142" t="n"/>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="B66" s="248" t="inlineStr">
         <is>
           <t>Июль</t>
         </is>
       </c>
-      <c r="C65" s="199" t="inlineStr">
-        <is>
-          <t>Кургузов Данил</t>
-        </is>
-      </c>
-      <c r="D65" s="202" t="n">
+      <c r="C66" s="248" t="inlineStr">
+        <is>
+          <t>Юлиана Юнусова</t>
+        </is>
+      </c>
+      <c r="D66" s="249" t="n">
         <v>350</v>
       </c>
-      <c r="E65" s="202" t="n">
-        <v>41</v>
-      </c>
-      <c r="F65" s="201">
-        <f>IF(OR(D65="",E65="",D65=0),"",E65/D65)</f>
-        <v/>
-      </c>
-      <c r="G65" s="202" t="n">
-        <v>17</v>
-      </c>
-      <c r="H65" s="201">
-        <f>IF(OR(E65="",G65="",E65=0),"",G65/E65)</f>
-        <v/>
-      </c>
-      <c r="I65" s="233" t="n">
-        <v>2</v>
-      </c>
-      <c r="J65" s="201">
-        <f>IF(OR(G65="",I65="",G65=0),"",I65/G65)</f>
-        <v/>
-      </c>
-      <c r="K65" s="234" t="n">
-        <v>1</v>
-      </c>
-      <c r="L65" s="203" t="inlineStr">
-        <is>
-          <t>KS аналитика (с 28.07); в ЗП июля нет строки</t>
-        </is>
-      </c>
-      <c r="M65" s="203" t="inlineStr">
-        <is>
-          <t>Неполный месяц (с 28.07). Результат: 1 запись на подкл. + 1 пробный (KS). Скрипт принят 100% (нет негативного контроля).</t>
-        </is>
-      </c>
-      <c r="N65" s="142" t="n"/>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="B66" s="204" t="inlineStr">
-        <is>
-          <t>Август</t>
-        </is>
-      </c>
-      <c r="C66" s="205" t="inlineStr">
-        <is>
-          <t>Юлиана Юнусова</t>
-        </is>
-      </c>
-      <c r="D66" s="202" t="n">
-        <v>350</v>
-      </c>
-      <c r="E66" s="202" t="n">
-        <v>352</v>
-      </c>
-      <c r="F66" s="201">
+      <c r="E66" s="249" t="n">
+        <v>433</v>
+      </c>
+      <c r="F66" s="250">
         <f>IF(OR(D66="",E66="",D66=0),"",E66/D66)</f>
         <v/>
       </c>
-      <c r="G66" s="202" t="n">
-        <v>15</v>
-      </c>
-      <c r="H66" s="201">
+      <c r="G66" s="249" t="n">
+        <v>32</v>
+      </c>
+      <c r="H66" s="250">
         <f>IF(OR(E66="",G66="",E66=0),"",G66/E66)</f>
         <v/>
       </c>
-      <c r="I66" s="202" t="n">
-        <v>28</v>
-      </c>
-      <c r="J66" s="201">
+      <c r="I66" s="249" t="n">
+        <v>19</v>
+      </c>
+      <c r="J66" s="250">
         <f>IF(OR(G66="",I66="",G66=0),"",I66/G66)</f>
         <v/>
       </c>
-      <c r="K66" s="209" t="n">
+      <c r="K66" s="251" t="n">
         <v>1</v>
       </c>
-      <c r="L66" s="208" t="inlineStr">
-        <is>
-          <t>ЗП звонки/скрипт; сделки=KS; результат=демо8+Доки9+Смартвей11</t>
-        </is>
-      </c>
-      <c r="M66" s="208" t="inlineStr">
-        <is>
-          <t>В сводке КабС демо указано 9; в ЗП KPI — 8</t>
+      <c r="L66" s="252" t="inlineStr">
+        <is>
+          <t>ЗП звонки/скрипт; сделки=DOKI+KS; результат=демо15+Доки4</t>
+        </is>
+      </c>
+      <c r="M66" s="252" t="inlineStr">
+        <is>
+          <t>КП 10/10 учтены отдельно в проектном блоке.</t>
         </is>
       </c>
       <c r="N66" s="142" t="n"/>
     </row>
-    <row r="67" ht="32" customHeight="1">
-      <c r="B67" s="198" t="inlineStr">
-        <is>
-          <t>Август</t>
-        </is>
-      </c>
-      <c r="C67" s="199" t="inlineStr">
+    <row r="67" ht="28" customHeight="1">
+      <c r="B67" s="248" t="inlineStr">
+        <is>
+          <t>Июль</t>
+        </is>
+      </c>
+      <c r="C67" s="248" t="inlineStr">
         <is>
           <t>Оглоблина Софья</t>
         </is>
       </c>
-      <c r="D67" s="202" t="n">
+      <c r="D67" s="249" t="n">
         <v>350</v>
       </c>
-      <c r="E67" s="202" t="n">
-        <v>481</v>
-      </c>
-      <c r="F67" s="201">
+      <c r="E67" s="249" t="n">
+        <v>383</v>
+      </c>
+      <c r="F67" s="250">
         <f>IF(OR(D67="",E67="",D67=0),"",E67/D67)</f>
         <v/>
       </c>
-      <c r="G67" s="202" t="n">
-        <v>23</v>
-      </c>
-      <c r="H67" s="201">
+      <c r="G67" s="249" t="n">
+        <v>16</v>
+      </c>
+      <c r="H67" s="250">
         <f>IF(OR(E67="",G67="",E67=0),"",G67/E67)</f>
         <v/>
       </c>
-      <c r="I67" s="202" t="n">
-        <v>12</v>
-      </c>
-      <c r="J67" s="201">
+      <c r="I67" s="249" t="n">
+        <v>5</v>
+      </c>
+      <c r="J67" s="250">
         <f>IF(OR(G67="",I67="",G67=0),"",I67/G67)</f>
         <v/>
       </c>
-      <c r="K67" s="209" t="n">
+      <c r="K67" s="251" t="n">
         <v>1</v>
       </c>
-      <c r="L67" s="203" t="inlineStr">
-        <is>
-          <t>ЗП; сделки=KS; результат=демо2+Доки1+Смартвей9</t>
-        </is>
-      </c>
-      <c r="M67" s="203" t="inlineStr"/>
+      <c r="L67" s="252" t="inlineStr">
+        <is>
+          <t>ЗП; сделки=DOKI+KS; результат=демо4+Доки1</t>
+        </is>
+      </c>
+      <c r="M67" s="252" t="inlineStr">
+        <is>
+          <t>КП 13/10.</t>
+        </is>
+      </c>
       <c r="N67" s="142" t="n"/>
     </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="B68" s="204" t="inlineStr">
-        <is>
-          <t>Август</t>
-        </is>
-      </c>
-      <c r="C68" s="205" t="inlineStr">
+    <row r="68" ht="28" customHeight="1">
+      <c r="B68" s="248" t="inlineStr">
+        <is>
+          <t>Июль</t>
+        </is>
+      </c>
+      <c r="C68" s="248" t="inlineStr">
         <is>
           <t>Кургузов Данил</t>
         </is>
       </c>
-      <c r="D68" s="202" t="n">
+      <c r="D68" s="249" t="n">
         <v>350</v>
       </c>
-      <c r="E68" s="202" t="n">
-        <v>395</v>
-      </c>
-      <c r="F68" s="201">
+      <c r="E68" s="249" t="n">
+        <v>41</v>
+      </c>
+      <c r="F68" s="250">
         <f>IF(OR(D68="",E68="",D68=0),"",E68/D68)</f>
         <v/>
       </c>
-      <c r="G68" s="233" t="n">
-        <v>18</v>
-      </c>
-      <c r="H68" s="201">
+      <c r="G68" s="249" t="n">
+        <v>17</v>
+      </c>
+      <c r="H68" s="250">
         <f>IF(OR(E68="",G68="",E68=0),"",G68/E68)</f>
         <v/>
       </c>
-      <c r="I68" s="202" t="n">
-        <v>14</v>
-      </c>
-      <c r="J68" s="201">
+      <c r="I68" s="249" t="n">
+        <v>2</v>
+      </c>
+      <c r="J68" s="250">
         <f>IF(OR(G68="",I68="",G68=0),"",I68/G68)</f>
         <v/>
       </c>
-      <c r="K68" s="234" t="n">
+      <c r="K68" s="251" t="n">
         <v>1</v>
       </c>
-      <c r="L68" s="208" t="inlineStr">
+      <c r="L68" s="252" t="inlineStr">
+        <is>
+          <t>KS аналитика (с 28.07); в ЗП июля нет строки</t>
+        </is>
+      </c>
+      <c r="M68" s="252" t="inlineStr">
+        <is>
+          <t>Неполный месяц (с 28.07). Результат: 1 запись на подкл. + 1 пробный (KS). Скрипт 100% (нет негативного контроля).</t>
+        </is>
+      </c>
+      <c r="N68" s="142" t="n"/>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="B69" s="248" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="C69" s="248" t="inlineStr">
+        <is>
+          <t>Юлиана Юнусова</t>
+        </is>
+      </c>
+      <c r="D69" s="249" t="n">
+        <v>350</v>
+      </c>
+      <c r="E69" s="249" t="n">
+        <v>352</v>
+      </c>
+      <c r="F69" s="250">
+        <f>IF(OR(D69="",E69="",D69=0),"",E69/D69)</f>
+        <v/>
+      </c>
+      <c r="G69" s="249" t="n">
+        <v>15</v>
+      </c>
+      <c r="H69" s="250">
+        <f>IF(OR(E69="",G69="",E69=0),"",G69/E69)</f>
+        <v/>
+      </c>
+      <c r="I69" s="249" t="n">
+        <v>28</v>
+      </c>
+      <c r="J69" s="250">
+        <f>IF(OR(G69="",I69="",G69=0),"",I69/G69)</f>
+        <v/>
+      </c>
+      <c r="K69" s="251" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" s="252" t="inlineStr">
+        <is>
+          <t>ЗП звонки/скрипт; сделки=KS; результат=демо8+Доки9+Смартвей11</t>
+        </is>
+      </c>
+      <c r="M69" s="252" t="inlineStr">
+        <is>
+          <t>В сводке КабС демо указано 9; в ЗП KPI — 8. Результат KPI &gt; сделок: разные контуры (демо/подкл./предложения).</t>
+        </is>
+      </c>
+      <c r="N69" s="142" t="n"/>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="B70" s="248" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="C70" s="248" t="inlineStr">
+        <is>
+          <t>Оглоблина Софья</t>
+        </is>
+      </c>
+      <c r="D70" s="249" t="n">
+        <v>350</v>
+      </c>
+      <c r="E70" s="249" t="n">
+        <v>481</v>
+      </c>
+      <c r="F70" s="250">
+        <f>IF(OR(D70="",E70="",D70=0),"",E70/D70)</f>
+        <v/>
+      </c>
+      <c r="G70" s="249" t="n">
+        <v>23</v>
+      </c>
+      <c r="H70" s="250">
+        <f>IF(OR(E70="",G70="",E70=0),"",G70/E70)</f>
+        <v/>
+      </c>
+      <c r="I70" s="249" t="n">
+        <v>12</v>
+      </c>
+      <c r="J70" s="250">
+        <f>IF(OR(G70="",I70="",G70=0),"",I70/G70)</f>
+        <v/>
+      </c>
+      <c r="K70" s="251" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="252" t="inlineStr">
+        <is>
+          <t>ЗП; сделки=KS; результат=демо2+Доки1+Смартвей9</t>
+        </is>
+      </c>
+      <c r="M70" s="252" t="inlineStr">
+        <is>
+          <t>Перевыполнение плана звонков. Конверсия в сделку ниже группы июля — холодный КабС.</t>
+        </is>
+      </c>
+      <c r="N70" s="142" t="n"/>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="B71" s="248" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="C71" s="248" t="inlineStr">
+        <is>
+          <t>Кургузов Данил</t>
+        </is>
+      </c>
+      <c r="D71" s="249" t="n">
+        <v>350</v>
+      </c>
+      <c r="E71" s="249" t="n">
+        <v>395</v>
+      </c>
+      <c r="F71" s="250">
+        <f>IF(OR(D71="",E71="",D71=0),"",E71/D71)</f>
+        <v/>
+      </c>
+      <c r="G71" s="249" t="n">
+        <v>18</v>
+      </c>
+      <c r="H71" s="250">
+        <f>IF(OR(E71="",G71="",E71=0),"",G71/E71)</f>
+        <v/>
+      </c>
+      <c r="I71" s="249" t="n">
+        <v>14</v>
+      </c>
+      <c r="J71" s="250">
+        <f>IF(OR(G71="",I71="",G71=0),"",I71/G71)</f>
+        <v/>
+      </c>
+      <c r="K71" s="251" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" s="252" t="inlineStr">
         <is>
           <t>KS звонки; результат=КабС2+Смартвей12</t>
         </is>
       </c>
-      <c r="M68" s="208" t="inlineStr">
-        <is>
-          <t>Сделки 18 восстановлены по конверсии группы в августе (~4.5–5% от 395 звонков). Результат=КабС 2 демо + Смартвей 12.</t>
-        </is>
-      </c>
-      <c r="N68" s="142" t="n"/>
-    </row>
-    <row r="69" ht="22.35" customHeight="1">
-      <c r="B69" s="210" t="n"/>
-      <c r="C69" s="210" t="n"/>
-      <c r="D69" s="210" t="n"/>
-      <c r="E69" s="210" t="n"/>
-      <c r="F69" s="210" t="n"/>
-      <c r="G69" s="210" t="n"/>
-      <c r="H69" s="210" t="n"/>
-      <c r="I69" s="210" t="n"/>
-      <c r="J69" s="210" t="n"/>
-      <c r="K69" s="211" t="n"/>
-      <c r="L69" s="212" t="n"/>
-      <c r="M69" s="194" t="n"/>
-      <c r="N69" s="142" t="n"/>
-    </row>
-    <row r="70" ht="22.35" customHeight="1">
-      <c r="B70" s="191" t="inlineStr">
+      <c r="M71" s="252" t="inlineStr">
+        <is>
+          <t>Сделки 18 восстановлены по конверсии группы в августе (~4,5% от 395). Поле KS «В сделку» было пустым.</t>
+        </is>
+      </c>
+      <c r="N71" s="142" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="B72" s="245" t="n"/>
+      <c r="C72" s="246" t="n"/>
+      <c r="D72" s="246" t="n"/>
+      <c r="E72" s="246" t="n"/>
+      <c r="F72" s="246" t="n"/>
+      <c r="G72" s="246" t="n"/>
+      <c r="H72" s="246" t="n"/>
+      <c r="I72" s="246" t="n"/>
+      <c r="J72" s="246" t="n"/>
+      <c r="K72" s="254" t="n"/>
+      <c r="L72" s="254" t="n"/>
+      <c r="M72" s="246" t="n"/>
+      <c r="N72" s="142" t="n"/>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="B73" s="255" t="inlineStr">
         <is>
           <t>ПРОЕКТНЫЕ KPI И КОНВЕРСИИ ПО МЕНЕДЖЕРАМ</t>
         </is>
       </c>
-      <c r="C70" s="231" t="n"/>
-      <c r="D70" s="231" t="n"/>
-      <c r="E70" s="231" t="n"/>
-      <c r="F70" s="231" t="n"/>
-      <c r="G70" s="231" t="n"/>
-      <c r="H70" s="231" t="n"/>
-      <c r="I70" s="231" t="n"/>
-      <c r="J70" s="231" t="n"/>
-      <c r="K70" s="231" t="n"/>
-      <c r="L70" s="231" t="n"/>
-      <c r="M70" s="232" t="n"/>
-      <c r="N70" s="142" t="n"/>
-    </row>
-    <row r="71" ht="36" customHeight="1">
-      <c r="B71" s="192" t="inlineStr">
-        <is>
-          <t>Один менеджер — несколько строк (по проектам). Конверсии: звонок→сделка и сделка→результат KPI. Звонки по проекту заполнены там, где аналитика однозначно относится к проекту (Доки / КабС); иначе — жёлтым (нужна разбивка по проектам).</t>
-        </is>
-      </c>
-      <c r="C71" s="231" t="n"/>
-      <c r="D71" s="231" t="n"/>
-      <c r="E71" s="231" t="n"/>
-      <c r="F71" s="231" t="n"/>
-      <c r="G71" s="231" t="n"/>
-      <c r="H71" s="231" t="n"/>
-      <c r="I71" s="231" t="n"/>
-      <c r="J71" s="231" t="n"/>
-      <c r="K71" s="231" t="n"/>
-      <c r="L71" s="231" t="n"/>
-      <c r="M71" s="232" t="n"/>
-      <c r="N71" s="142" t="n"/>
-    </row>
-    <row r="72" ht="22.35" customHeight="1">
-      <c r="B72" s="193" t="n"/>
-      <c r="C72" s="194" t="n"/>
-      <c r="D72" s="194" t="n"/>
-      <c r="E72" s="194" t="n"/>
-      <c r="F72" s="194" t="n"/>
-      <c r="G72" s="194" t="n"/>
-      <c r="H72" s="194" t="n"/>
-      <c r="I72" s="194" t="n"/>
-      <c r="J72" s="194" t="n"/>
-      <c r="K72" s="211" t="n"/>
-      <c r="L72" s="212" t="n"/>
-      <c r="M72" s="194" t="n"/>
-      <c r="N72" s="142" t="n"/>
-    </row>
-    <row r="73" ht="22.35" customHeight="1">
-      <c r="B73" s="196" t="inlineStr">
+      <c r="C73" s="95" t="n"/>
+      <c r="D73" s="95" t="n"/>
+      <c r="E73" s="95" t="n"/>
+      <c r="F73" s="95" t="n"/>
+      <c r="G73" s="95" t="n"/>
+      <c r="H73" s="95" t="n"/>
+      <c r="I73" s="95" t="n"/>
+      <c r="J73" s="95" t="n"/>
+      <c r="K73" s="95" t="n"/>
+      <c r="L73" s="95" t="n"/>
+      <c r="M73" s="95" t="n"/>
+      <c r="N73" s="142" t="n"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="B74" s="256" t="inlineStr">
+        <is>
+          <t>Один менеджер — несколько строк (по проектам). Конверсии — формулы в строке. Звонки по проекту: Доки/КабС из дневников; Смартвей и часть августа — оценка доли (жёлтый).</t>
+        </is>
+      </c>
+      <c r="C74" s="95" t="n"/>
+      <c r="D74" s="95" t="n"/>
+      <c r="E74" s="95" t="n"/>
+      <c r="F74" s="95" t="n"/>
+      <c r="G74" s="95" t="n"/>
+      <c r="H74" s="95" t="n"/>
+      <c r="I74" s="95" t="n"/>
+      <c r="J74" s="95" t="n"/>
+      <c r="K74" s="95" t="n"/>
+      <c r="L74" s="95" t="n"/>
+      <c r="M74" s="95" t="n"/>
+      <c r="N74" s="142" t="n"/>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="B75" s="239" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="C73" s="196" t="inlineStr">
+      <c r="C75" s="239" t="inlineStr">
         <is>
           <t>Проект</t>
         </is>
       </c>
-      <c r="D73" s="213" t="inlineStr">
+      <c r="D75" s="239" t="inlineStr">
         <is>
           <t>Менеджер</t>
         </is>
       </c>
-      <c r="E73" s="213" t="inlineStr">
+      <c r="E75" s="239" t="inlineStr">
         <is>
           <t>KPI проекта</t>
         </is>
       </c>
-      <c r="F73" s="213" t="inlineStr">
+      <c r="F75" s="239" t="inlineStr">
         <is>
           <t>План KPI</t>
         </is>
       </c>
-      <c r="G73" s="213" t="inlineStr">
+      <c r="G75" s="239" t="inlineStr">
         <is>
           <t>Факт KPI</t>
         </is>
       </c>
-      <c r="H73" s="196" t="inlineStr">
+      <c r="H75" s="239" t="inlineStr">
         <is>
           <t>Выполнение KPI</t>
         </is>
       </c>
-      <c r="I73" s="196" t="inlineStr">
+      <c r="I75" s="239" t="inlineStr">
         <is>
           <t>Звонки по проекту</t>
         </is>
       </c>
-      <c r="J73" s="196" t="inlineStr">
+      <c r="J75" s="239" t="inlineStr">
         <is>
           <t>Сделки</t>
         </is>
       </c>
-      <c r="K73" s="196" t="inlineStr">
+      <c r="K75" s="239" t="inlineStr">
         <is>
           <t>Конв. звонок → сделка</t>
         </is>
       </c>
-      <c r="L73" s="214" t="inlineStr">
+      <c r="L75" s="239" t="inlineStr">
         <is>
           <t>Конв. сделка → результат</t>
         </is>
       </c>
-      <c r="M73" s="196" t="inlineStr">
+      <c r="M75" s="239" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
-      <c r="N73" s="142" t="n"/>
-    </row>
-    <row r="74" ht="28" customHeight="1">
-      <c r="B74" s="198" t="inlineStr">
+      <c r="N75" s="142" t="n"/>
+    </row>
+    <row r="76" ht="26" customHeight="1">
+      <c r="B76" s="257" t="inlineStr">
         <is>
           <t>Июнь</t>
         </is>
       </c>
-      <c r="C74" s="199" t="inlineStr">
+      <c r="C76" s="257" t="inlineStr">
         <is>
           <t>Доки</t>
         </is>
       </c>
-      <c r="D74" s="215" t="inlineStr">
+      <c r="D76" s="257" t="inlineStr">
         <is>
           <t>Юлиана Юнусова</t>
         </is>
       </c>
-      <c r="E74" s="215" t="inlineStr">
+      <c r="E76" s="257" t="inlineStr">
         <is>
           <t>Подключения (группа)</t>
         </is>
       </c>
-      <c r="F74" s="216" t="n">
+      <c r="F76" s="258" t="n">
         <v>2</v>
       </c>
-      <c r="G74" s="216" t="n">
+      <c r="G76" s="258" t="n">
         <v>1</v>
       </c>
-      <c r="H74" s="201">
-        <f>IF(OR(F74="",G74="",F74=0),"",G74/F74)</f>
-        <v/>
-      </c>
-      <c r="I74" s="236" t="n">
-        <v>86</v>
-      </c>
-      <c r="J74" s="236" t="n">
-        <v>4</v>
-      </c>
-      <c r="K74" s="201">
-        <f>IF(OR(I74="",J74="",I74=0),"",J74/I74)</f>
-        <v/>
-      </c>
-      <c r="L74" s="201">
-        <f>IF(OR(J74="",G74="",J74=0),"",G74/J74)</f>
-        <v/>
-      </c>
-      <c r="M74" s="203" t="inlineStr">
-        <is>
-          <t>ЗП: групповой KPI 1 подключение. Звонки/сделки — оценка доли июня на Доки.</t>
-        </is>
-      </c>
-      <c r="N74" s="142" t="n"/>
-    </row>
-    <row r="75" ht="28" customHeight="1">
-      <c r="B75" s="204" t="inlineStr">
-        <is>
-          <t>Июнь</t>
-        </is>
-      </c>
-      <c r="C75" s="205" t="inlineStr">
-        <is>
-          <t>Доки</t>
-        </is>
-      </c>
-      <c r="D75" s="218" t="inlineStr">
-        <is>
-          <t>Оглоблина Софья</t>
-        </is>
-      </c>
-      <c r="E75" s="218" t="inlineStr">
-        <is>
-          <t>Подключения (группа)</t>
-        </is>
-      </c>
-      <c r="F75" s="216" t="n">
-        <v>2</v>
-      </c>
-      <c r="G75" s="219" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="201">
-        <f>IF(OR(F75="",G75="",F75=0),"",G75/F75)</f>
-        <v/>
-      </c>
-      <c r="I75" s="236" t="n">
-        <v>94</v>
-      </c>
-      <c r="J75" s="234" t="n">
-        <v>3</v>
-      </c>
-      <c r="K75" s="201">
-        <f>IF(OR(I75="",J75="",I75=0),"",J75/I75)</f>
-        <v/>
-      </c>
-      <c r="L75" s="201">
-        <f>IF(OR(J75="",G75="",J75=0),"",G75/J75)</f>
-        <v/>
-      </c>
-      <c r="M75" s="208" t="inlineStr">
-        <is>
-          <t>ЗП: групповой KPI. Звонки/сделки — оценка доли июня на Доки.</t>
-        </is>
-      </c>
-      <c r="N75" s="142" t="n"/>
-    </row>
-    <row r="76" ht="28" customHeight="1">
-      <c r="B76" s="198" t="inlineStr">
-        <is>
-          <t>Июль</t>
-        </is>
-      </c>
-      <c r="C76" s="199" t="inlineStr">
-        <is>
-          <t>Доки</t>
-        </is>
-      </c>
-      <c r="D76" s="215" t="inlineStr">
-        <is>
-          <t>Юлиана Юнусова</t>
-        </is>
-      </c>
-      <c r="E76" s="215" t="inlineStr">
-        <is>
-          <t>Подключения</t>
-        </is>
-      </c>
-      <c r="F76" s="216" t="n">
-        <v>8</v>
-      </c>
-      <c r="G76" s="219" t="n">
-        <v>4</v>
-      </c>
-      <c r="H76" s="201">
+      <c r="H76" s="259">
         <f>IF(OR(F76="",G76="",F76=0),"",G76/F76)</f>
         <v/>
       </c>
-      <c r="I76" s="216" t="n">
-        <v>179</v>
-      </c>
-      <c r="J76" s="219" t="n">
-        <v>22</v>
-      </c>
-      <c r="K76" s="201">
+      <c r="I76" s="260" t="n">
+        <v>86</v>
+      </c>
+      <c r="J76" s="260" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" s="259">
         <f>IF(OR(I76="",J76="",I76=0),"",J76/I76)</f>
         <v/>
       </c>
-      <c r="L76" s="201">
+      <c r="L76" s="259">
         <f>IF(OR(J76="",G76="",J76=0),"",G76/J76)</f>
         <v/>
       </c>
-      <c r="M76" s="203" t="inlineStr">
-        <is>
-          <t>ЗП KPI; звонки/сделки — DOKI_analitika</t>
+      <c r="M76" s="261" t="inlineStr">
+        <is>
+          <t>ЗП: групповой KPI 1 подключение. Звонки/сделки — оценка доли июня на Доки.</t>
         </is>
       </c>
       <c r="N76" s="142" t="n"/>
     </row>
-    <row r="77" ht="28" customHeight="1">
-      <c r="B77" s="204" t="inlineStr">
-        <is>
-          <t>Июль</t>
-        </is>
-      </c>
-      <c r="C77" s="205" t="inlineStr">
+    <row r="77" ht="26" customHeight="1">
+      <c r="B77" s="257" t="inlineStr">
+        <is>
+          <t>Июнь</t>
+        </is>
+      </c>
+      <c r="C77" s="257" t="inlineStr">
         <is>
           <t>Доки</t>
         </is>
       </c>
-      <c r="D77" s="218" t="inlineStr">
+      <c r="D77" s="257" t="inlineStr">
         <is>
           <t>Оглоблина Софья</t>
         </is>
       </c>
-      <c r="E77" s="218" t="inlineStr">
-        <is>
-          <t>Подключения</t>
-        </is>
-      </c>
-      <c r="F77" s="216" t="n">
-        <v>8</v>
-      </c>
-      <c r="G77" s="219" t="n">
+      <c r="E77" s="257" t="inlineStr">
+        <is>
+          <t>Подключения (группа)</t>
+        </is>
+      </c>
+      <c r="F77" s="258" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" s="258" t="n">
         <v>1</v>
       </c>
-      <c r="H77" s="201">
+      <c r="H77" s="259">
         <f>IF(OR(F77="",G77="",F77=0),"",G77/F77)</f>
         <v/>
       </c>
-      <c r="I77" s="216" t="n">
-        <v>198</v>
-      </c>
-      <c r="J77" s="219" t="n">
-        <v>8</v>
-      </c>
-      <c r="K77" s="201">
+      <c r="I77" s="260" t="n">
+        <v>94</v>
+      </c>
+      <c r="J77" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="K77" s="259">
         <f>IF(OR(I77="",J77="",I77=0),"",J77/I77)</f>
         <v/>
       </c>
-      <c r="L77" s="201">
+      <c r="L77" s="259">
         <f>IF(OR(J77="",G77="",J77=0),"",G77/J77)</f>
         <v/>
       </c>
-      <c r="M77" s="208" t="inlineStr">
-        <is>
-          <t>ЗП KPI; звонки/сделки — DOKI_analitika</t>
+      <c r="M77" s="261" t="inlineStr">
+        <is>
+          <t>ЗП: групповой KPI. Звонки/сделки — оценка доли июня на Доки.</t>
         </is>
       </c>
       <c r="N77" s="142" t="n"/>
     </row>
-    <row r="78" ht="28" customHeight="1">
-      <c r="B78" s="198" t="inlineStr">
+    <row r="78" ht="26" customHeight="1">
+      <c r="B78" s="257" t="inlineStr">
         <is>
           <t>Июль</t>
         </is>
       </c>
-      <c r="C78" s="199" t="inlineStr">
+      <c r="C78" s="257" t="inlineStr">
         <is>
           <t>Доки</t>
         </is>
       </c>
-      <c r="D78" s="215" t="inlineStr">
-        <is>
-          <t>Кургузов Данил</t>
-        </is>
-      </c>
-      <c r="E78" s="215" t="inlineStr">
+      <c r="D78" s="257" t="inlineStr">
+        <is>
+          <t>Юлиана Юнусова</t>
+        </is>
+      </c>
+      <c r="E78" s="257" t="inlineStr">
         <is>
           <t>Подключения</t>
         </is>
       </c>
-      <c r="F78" s="216" t="n">
+      <c r="F78" s="258" t="n">
         <v>8</v>
       </c>
-      <c r="G78" s="234" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="201">
+      <c r="G78" s="258" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" s="259">
         <f>IF(OR(F78="",G78="",F78=0),"",G78/F78)</f>
         <v/>
       </c>
-      <c r="I78" s="236" t="n">
-        <v>14</v>
-      </c>
-      <c r="J78" s="234" t="n">
-        <v>1</v>
-      </c>
-      <c r="K78" s="201">
+      <c r="I78" s="258" t="n">
+        <v>179</v>
+      </c>
+      <c r="J78" s="258" t="n">
+        <v>22</v>
+      </c>
+      <c r="K78" s="259">
         <f>IF(OR(I78="",J78="",I78=0),"",J78/I78)</f>
         <v/>
       </c>
-      <c r="L78" s="201">
+      <c r="L78" s="259">
         <f>IF(OR(J78="",G78="",J78=0),"",G78/J78)</f>
         <v/>
       </c>
-      <c r="M78" s="203" t="inlineStr">
-        <is>
-          <t>В ЗП июля нет строки. Звонки/1 сделка — оценка конца июля; подключений 0.</t>
+      <c r="M78" s="261" t="inlineStr">
+        <is>
+          <t>ЗП KPI; звонки/сделки — DOKI_analitika.</t>
         </is>
       </c>
       <c r="N78" s="142" t="n"/>
     </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="B79" s="204" t="inlineStr">
+    <row r="79" ht="26" customHeight="1">
+      <c r="B79" s="257" t="inlineStr">
         <is>
           <t>Июль</t>
         </is>
       </c>
-      <c r="C79" s="205" t="inlineStr">
-        <is>
-          <t>Кабинет сотрудника</t>
-        </is>
-      </c>
-      <c r="D79" s="205" t="inlineStr">
-        <is>
-          <t>Юлиана Юнусова</t>
-        </is>
-      </c>
-      <c r="E79" s="205" t="inlineStr">
-        <is>
-          <t>Демонстрации</t>
-        </is>
-      </c>
-      <c r="F79" s="202" t="n">
-        <v>15</v>
-      </c>
-      <c r="G79" s="219" t="n">
-        <v>15</v>
-      </c>
-      <c r="H79" s="201">
+      <c r="C79" s="257" t="inlineStr">
+        <is>
+          <t>Доки</t>
+        </is>
+      </c>
+      <c r="D79" s="257" t="inlineStr">
+        <is>
+          <t>Оглоблина Софья</t>
+        </is>
+      </c>
+      <c r="E79" s="257" t="inlineStr">
+        <is>
+          <t>Подключения</t>
+        </is>
+      </c>
+      <c r="F79" s="258" t="n">
+        <v>8</v>
+      </c>
+      <c r="G79" s="258" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="259">
         <f>IF(OR(F79="",G79="",F79=0),"",G79/F79)</f>
         <v/>
       </c>
-      <c r="I79" s="216" t="n">
-        <v>46</v>
-      </c>
-      <c r="J79" s="219" t="n">
-        <v>10</v>
-      </c>
-      <c r="K79" s="201">
+      <c r="I79" s="258" t="n">
+        <v>198</v>
+      </c>
+      <c r="J79" s="258" t="n">
+        <v>8</v>
+      </c>
+      <c r="K79" s="259">
         <f>IF(OR(I79="",J79="",I79=0),"",J79/I79)</f>
         <v/>
       </c>
-      <c r="L79" s="201">
+      <c r="L79" s="259">
         <f>IF(OR(J79="",G79="",J79=0),"",G79/J79)</f>
         <v/>
       </c>
-      <c r="M79" s="208" t="inlineStr">
-        <is>
-          <t>ЗП демо; звонки/сделки — KS июль</t>
+      <c r="M79" s="261" t="inlineStr">
+        <is>
+          <t>ЗП KPI; звонки/сделки — DOKI_analitika.</t>
         </is>
       </c>
       <c r="N79" s="142" t="n"/>
     </row>
-    <row r="80" ht="28" customHeight="1">
-      <c r="B80" s="198" t="inlineStr">
+    <row r="80" ht="26" customHeight="1">
+      <c r="B80" s="257" t="inlineStr">
         <is>
           <t>Июль</t>
         </is>
       </c>
-      <c r="C80" s="199" t="inlineStr">
-        <is>
-          <t>Кабинет сотрудника</t>
-        </is>
-      </c>
-      <c r="D80" s="199" t="inlineStr">
-        <is>
-          <t>Оглоблина Софья</t>
-        </is>
-      </c>
-      <c r="E80" s="199" t="inlineStr">
-        <is>
-          <t>Демонстрации</t>
-        </is>
-      </c>
-      <c r="F80" s="202" t="n">
-        <v>15</v>
-      </c>
-      <c r="G80" s="219" t="n">
-        <v>4</v>
-      </c>
-      <c r="H80" s="201">
+      <c r="C80" s="257" t="inlineStr">
+        <is>
+          <t>Доки</t>
+        </is>
+      </c>
+      <c r="D80" s="257" t="inlineStr">
+        <is>
+          <t>Кургузов Данил</t>
+        </is>
+      </c>
+      <c r="E80" s="257" t="inlineStr">
+        <is>
+          <t>Подключения</t>
+        </is>
+      </c>
+      <c r="F80" s="258" t="n">
+        <v>8</v>
+      </c>
+      <c r="G80" s="258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="259">
         <f>IF(OR(F80="",G80="",F80=0),"",G80/F80)</f>
         <v/>
       </c>
-      <c r="I80" s="202" t="n">
-        <v>121</v>
-      </c>
-      <c r="J80" s="219" t="n">
-        <v>8</v>
-      </c>
-      <c r="K80" s="201">
+      <c r="I80" s="260" t="n">
+        <v>14</v>
+      </c>
+      <c r="J80" s="260" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" s="259">
         <f>IF(OR(I80="",J80="",I80=0),"",J80/I80)</f>
         <v/>
       </c>
-      <c r="L80" s="201">
+      <c r="L80" s="259">
         <f>IF(OR(J80="",G80="",J80=0),"",G80/J80)</f>
         <v/>
       </c>
-      <c r="M80" s="203" t="inlineStr">
-        <is>
-          <t>ЗП демо; звонки/сделки — KS июль</t>
+      <c r="M80" s="261" t="inlineStr">
+        <is>
+          <t>В ЗП июля нет строки. Звонки/1 сделка — оценка конца июля; подключений 0.</t>
         </is>
       </c>
       <c r="N80" s="142" t="n"/>
     </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="B81" s="204" t="inlineStr">
+    <row r="81" ht="26" customHeight="1">
+      <c r="B81" s="257" t="inlineStr">
         <is>
           <t>Июль</t>
         </is>
       </c>
-      <c r="C81" s="205" t="inlineStr">
+      <c r="C81" s="257" t="inlineStr">
         <is>
           <t>Кабинет сотрудника</t>
         </is>
       </c>
-      <c r="D81" s="205" t="inlineStr">
-        <is>
-          <t>Кургузов Данил</t>
-        </is>
-      </c>
-      <c r="E81" s="205" t="inlineStr">
+      <c r="D81" s="257" t="inlineStr">
+        <is>
+          <t>Юлиана Юнусова</t>
+        </is>
+      </c>
+      <c r="E81" s="257" t="inlineStr">
         <is>
           <t>Демонстрации</t>
         </is>
       </c>
-      <c r="F81" s="233" t="n">
+      <c r="F81" s="258" t="n">
         <v>15</v>
       </c>
-      <c r="G81" s="234" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" s="201">
+      <c r="G81" s="258" t="n">
+        <v>15</v>
+      </c>
+      <c r="H81" s="259">
         <f>IF(OR(F81="",G81="",F81=0),"",G81/F81)</f>
         <v/>
       </c>
-      <c r="I81" s="202" t="n">
-        <v>41</v>
-      </c>
-      <c r="J81" s="219" t="n">
-        <v>17</v>
-      </c>
-      <c r="K81" s="201">
+      <c r="I81" s="258" t="n">
+        <v>46</v>
+      </c>
+      <c r="J81" s="258" t="n">
+        <v>10</v>
+      </c>
+      <c r="K81" s="259">
         <f>IF(OR(I81="",J81="",I81=0),"",J81/I81)</f>
         <v/>
       </c>
-      <c r="L81" s="201">
+      <c r="L81" s="259">
         <f>IF(OR(J81="",G81="",J81=0),"",G81/J81)</f>
         <v/>
       </c>
-      <c r="M81" s="208" t="inlineStr">
-        <is>
-          <t>KS с 28.07: 41 звонок, 17 сделок; демо/пробный 1. План демо как у группы (15).</t>
+      <c r="M81" s="261" t="inlineStr">
+        <is>
+          <t>ЗП демо; звонки/сделки — KS июль.</t>
         </is>
       </c>
       <c r="N81" s="142" t="n"/>
     </row>
-    <row r="82" ht="28" customHeight="1">
-      <c r="B82" s="198" t="inlineStr">
-        <is>
-          <t>Август</t>
-        </is>
-      </c>
-      <c r="C82" s="199" t="inlineStr">
+    <row r="82" ht="26" customHeight="1">
+      <c r="B82" s="257" t="inlineStr">
+        <is>
+          <t>Июль</t>
+        </is>
+      </c>
+      <c r="C82" s="257" t="inlineStr">
         <is>
           <t>Кабинет сотрудника</t>
         </is>
       </c>
-      <c r="D82" s="199" t="inlineStr">
-        <is>
-          <t>Юлиана Юнусова</t>
-        </is>
-      </c>
-      <c r="E82" s="199" t="inlineStr">
+      <c r="D82" s="257" t="inlineStr">
+        <is>
+          <t>Оглоблина Софья</t>
+        </is>
+      </c>
+      <c r="E82" s="257" t="inlineStr">
         <is>
           <t>Демонстрации</t>
         </is>
       </c>
-      <c r="F82" s="202" t="n">
-        <v>10</v>
-      </c>
-      <c r="G82" s="219" t="n">
-        <v>8</v>
-      </c>
-      <c r="H82" s="201">
+      <c r="F82" s="258" t="n">
+        <v>15</v>
+      </c>
+      <c r="G82" s="258" t="n">
+        <v>4</v>
+      </c>
+      <c r="H82" s="259">
         <f>IF(OR(F82="",G82="",F82=0),"",G82/F82)</f>
         <v/>
       </c>
-      <c r="I82" s="202" t="n">
-        <v>98</v>
-      </c>
-      <c r="J82" s="219" t="n">
-        <v>15</v>
-      </c>
-      <c r="K82" s="201">
+      <c r="I82" s="258" t="n">
+        <v>121</v>
+      </c>
+      <c r="J82" s="258" t="n">
+        <v>8</v>
+      </c>
+      <c r="K82" s="259">
         <f>IF(OR(I82="",J82="",I82=0),"",J82/I82)</f>
         <v/>
       </c>
-      <c r="L82" s="201">
+      <c r="L82" s="259">
         <f>IF(OR(J82="",G82="",J82=0),"",G82/J82)</f>
         <v/>
       </c>
-      <c r="M82" s="203" t="inlineStr">
-        <is>
-          <t>ЗП KPI=8; сводка ЦКП=9; звонки/сделки KS август</t>
+      <c r="M82" s="261" t="inlineStr">
+        <is>
+          <t>ЗП демо 4/15; звонки/сделки — KS июль.</t>
         </is>
       </c>
       <c r="N82" s="142" t="n"/>
     </row>
-    <row r="83" ht="28" customHeight="1">
-      <c r="B83" s="204" t="inlineStr">
-        <is>
-          <t>Август</t>
-        </is>
-      </c>
-      <c r="C83" s="205" t="inlineStr">
+    <row r="83" ht="26" customHeight="1">
+      <c r="B83" s="257" t="inlineStr">
+        <is>
+          <t>Июль</t>
+        </is>
+      </c>
+      <c r="C83" s="257" t="inlineStr">
         <is>
           <t>Кабинет сотрудника</t>
         </is>
       </c>
-      <c r="D83" s="205" t="inlineStr">
-        <is>
-          <t>Оглоблина Софья</t>
-        </is>
-      </c>
-      <c r="E83" s="205" t="inlineStr">
+      <c r="D83" s="257" t="inlineStr">
+        <is>
+          <t>Кургузов Данил</t>
+        </is>
+      </c>
+      <c r="E83" s="257" t="inlineStr">
         <is>
           <t>Демонстрации</t>
         </is>
       </c>
-      <c r="F83" s="202" t="n">
-        <v>10</v>
-      </c>
-      <c r="G83" s="219" t="n">
-        <v>2</v>
-      </c>
-      <c r="H83" s="201">
+      <c r="F83" s="258" t="n">
+        <v>15</v>
+      </c>
+      <c r="G83" s="258" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="259">
         <f>IF(OR(F83="",G83="",F83=0),"",G83/F83)</f>
         <v/>
       </c>
-      <c r="I83" s="202" t="n">
-        <v>545</v>
-      </c>
-      <c r="J83" s="219" t="n">
-        <v>23</v>
-      </c>
-      <c r="K83" s="201">
+      <c r="I83" s="258" t="n">
+        <v>41</v>
+      </c>
+      <c r="J83" s="258" t="n">
+        <v>17</v>
+      </c>
+      <c r="K83" s="259">
         <f>IF(OR(I83="",J83="",I83=0),"",J83/I83)</f>
         <v/>
       </c>
-      <c r="L83" s="201">
+      <c r="L83" s="259">
         <f>IF(OR(J83="",G83="",J83=0),"",G83/J83)</f>
         <v/>
       </c>
-      <c r="M83" s="208" t="inlineStr">
-        <is>
-          <t>ЗП; KS август (возможны звонки и по другим темам)</t>
+      <c r="M83" s="261" t="inlineStr">
+        <is>
+          <t>KS с 28.07: звонки 41, сделки 17, демо/записи 1–2.</t>
         </is>
       </c>
       <c r="N83" s="142" t="n"/>
     </row>
-    <row r="84" ht="28" customHeight="1">
-      <c r="B84" s="198" t="inlineStr">
+    <row r="84" ht="26" customHeight="1">
+      <c r="B84" s="257" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
       </c>
-      <c r="C84" s="199" t="inlineStr">
+      <c r="C84" s="257" t="inlineStr">
         <is>
           <t>Кабинет сотрудника</t>
         </is>
       </c>
-      <c r="D84" s="199" t="inlineStr">
-        <is>
-          <t>Кургузов Данил</t>
-        </is>
-      </c>
-      <c r="E84" s="199" t="inlineStr">
+      <c r="D84" s="257" t="inlineStr">
+        <is>
+          <t>Юлиана Юнусова</t>
+        </is>
+      </c>
+      <c r="E84" s="257" t="inlineStr">
         <is>
           <t>Демонстрации</t>
         </is>
       </c>
-      <c r="F84" s="202" t="n">
+      <c r="F84" s="258" t="n">
         <v>10</v>
       </c>
-      <c r="G84" s="219" t="n">
-        <v>2</v>
-      </c>
-      <c r="H84" s="201">
+      <c r="G84" s="258" t="n">
+        <v>8</v>
+      </c>
+      <c r="H84" s="259">
         <f>IF(OR(F84="",G84="",F84=0),"",G84/F84)</f>
         <v/>
       </c>
-      <c r="I84" s="202" t="n">
-        <v>395</v>
-      </c>
-      <c r="J84" s="234" t="n">
-        <v>8</v>
-      </c>
-      <c r="K84" s="201">
+      <c r="I84" s="258" t="n">
+        <v>98</v>
+      </c>
+      <c r="J84" s="258" t="n">
+        <v>15</v>
+      </c>
+      <c r="K84" s="259">
         <f>IF(OR(I84="",J84="",I84=0),"",J84/I84)</f>
         <v/>
       </c>
-      <c r="L84" s="201">
+      <c r="L84" s="259">
         <f>IF(OR(J84="",G84="",J84=0),"",G84/J84)</f>
         <v/>
       </c>
-      <c r="M84" s="203" t="inlineStr">
-        <is>
-          <t>Факт демо из сводки ЦКП; сделки 8 восстановлены (доля КабС в августовских 18 сделках).</t>
+      <c r="M84" s="261" t="inlineStr">
+        <is>
+          <t>ЗП KPI=8; сводка ЦКП=9; звонки/сделки KS август.</t>
         </is>
       </c>
       <c r="N84" s="142" t="n"/>
     </row>
-    <row r="85" ht="28" customHeight="1">
-      <c r="B85" s="204" t="inlineStr">
+    <row r="85" ht="26" customHeight="1">
+      <c r="B85" s="257" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
       </c>
-      <c r="C85" s="205" t="inlineStr">
-        <is>
-          <t>Смартвей</t>
-        </is>
-      </c>
-      <c r="D85" s="205" t="inlineStr">
-        <is>
-          <t>Юлиана Юнусова</t>
-        </is>
-      </c>
-      <c r="E85" s="205" t="inlineStr">
-        <is>
-          <t>Предложения</t>
-        </is>
-      </c>
-      <c r="F85" s="202" t="n">
+      <c r="C85" s="257" t="inlineStr">
+        <is>
+          <t>Кабинет сотрудника</t>
+        </is>
+      </c>
+      <c r="D85" s="257" t="inlineStr">
+        <is>
+          <t>Оглоблина Софья</t>
+        </is>
+      </c>
+      <c r="E85" s="257" t="inlineStr">
+        <is>
+          <t>Демонстрации</t>
+        </is>
+      </c>
+      <c r="F85" s="258" t="n">
         <v>10</v>
       </c>
-      <c r="G85" s="219" t="n">
-        <v>11</v>
-      </c>
-      <c r="H85" s="201">
+      <c r="G85" s="258" t="n">
+        <v>2</v>
+      </c>
+      <c r="H85" s="259">
         <f>IF(OR(F85="",G85="",F85=0),"",G85/F85)</f>
         <v/>
       </c>
-      <c r="I85" s="233" t="n">
-        <v>68</v>
-      </c>
-      <c r="J85" s="234" t="n">
-        <v>9</v>
-      </c>
-      <c r="K85" s="201">
+      <c r="I85" s="258" t="n">
+        <v>545</v>
+      </c>
+      <c r="J85" s="258" t="n">
+        <v>23</v>
+      </c>
+      <c r="K85" s="259">
         <f>IF(OR(I85="",J85="",I85=0),"",J85/I85)</f>
         <v/>
       </c>
-      <c r="L85" s="201">
+      <c r="L85" s="259">
         <f>IF(OR(J85="",G85="",J85=0),"",G85/J85)</f>
         <v/>
       </c>
-      <c r="M85" s="208" t="inlineStr">
-        <is>
-          <t>Сводка ЦКП: 11 предложений. Звонки/сделки по Смартвей восстановлены (нет отдельной аналитики).</t>
+      <c r="M85" s="261" t="inlineStr">
+        <is>
+          <t>ЗП; KS август (возможны звонки и по другим темам).</t>
         </is>
       </c>
       <c r="N85" s="142" t="n"/>
     </row>
-    <row r="86" ht="28" customHeight="1">
-      <c r="B86" s="198" t="inlineStr">
+    <row r="86" ht="26" customHeight="1">
+      <c r="B86" s="257" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
       </c>
-      <c r="C86" s="199" t="inlineStr">
-        <is>
-          <t>Смартвей</t>
-        </is>
-      </c>
-      <c r="D86" s="199" t="inlineStr">
-        <is>
-          <t>Оглоблина Софья</t>
-        </is>
-      </c>
-      <c r="E86" s="199" t="inlineStr">
-        <is>
-          <t>Предложения</t>
-        </is>
-      </c>
-      <c r="F86" s="202" t="n">
+      <c r="C86" s="257" t="inlineStr">
+        <is>
+          <t>Кабинет сотрудника</t>
+        </is>
+      </c>
+      <c r="D86" s="257" t="inlineStr">
+        <is>
+          <t>Кургузов Данил</t>
+        </is>
+      </c>
+      <c r="E86" s="257" t="inlineStr">
+        <is>
+          <t>Демонстрации</t>
+        </is>
+      </c>
+      <c r="F86" s="258" t="n">
         <v>10</v>
       </c>
-      <c r="G86" s="219" t="n">
-        <v>9</v>
-      </c>
-      <c r="H86" s="201">
+      <c r="G86" s="258" t="n">
+        <v>2</v>
+      </c>
+      <c r="H86" s="259">
         <f>IF(OR(F86="",G86="",F86=0),"",G86/F86)</f>
         <v/>
       </c>
-      <c r="I86" s="233" t="n">
-        <v>61</v>
-      </c>
-      <c r="J86" s="234" t="n">
-        <v>7</v>
-      </c>
-      <c r="K86" s="201">
+      <c r="I86" s="260" t="n">
+        <v>395</v>
+      </c>
+      <c r="J86" s="260" t="n">
+        <v>8</v>
+      </c>
+      <c r="K86" s="259">
         <f>IF(OR(I86="",J86="",I86=0),"",J86/I86)</f>
         <v/>
       </c>
-      <c r="L86" s="201">
+      <c r="L86" s="259">
         <f>IF(OR(J86="",G86="",J86=0),"",G86/J86)</f>
         <v/>
       </c>
-      <c r="M86" s="203" t="inlineStr">
-        <is>
-          <t>Сводка ЦКП: 9 предложений. Звонки/сделки восстановлены.</t>
+      <c r="M86" s="261" t="inlineStr">
+        <is>
+          <t>Факт демо из сводки ЦКП; сделки 8 — доля КабС в 18 августовских сделках.</t>
         </is>
       </c>
       <c r="N86" s="142" t="n"/>
     </row>
-    <row r="87" ht="28" customHeight="1">
-      <c r="B87" s="204" t="inlineStr">
+    <row r="87" ht="26" customHeight="1">
+      <c r="B87" s="257" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
       </c>
-      <c r="C87" s="205" t="inlineStr">
+      <c r="C87" s="257" t="inlineStr">
         <is>
           <t>Смартвей</t>
         </is>
       </c>
-      <c r="D87" s="205" t="inlineStr">
-        <is>
-          <t>Кургузов Данил</t>
-        </is>
-      </c>
-      <c r="E87" s="205" t="inlineStr">
+      <c r="D87" s="257" t="inlineStr">
+        <is>
+          <t>Юлиана Юнусова</t>
+        </is>
+      </c>
+      <c r="E87" s="257" t="inlineStr">
         <is>
           <t>Предложения</t>
         </is>
       </c>
-      <c r="F87" s="202" t="n">
+      <c r="F87" s="258" t="n">
         <v>10</v>
       </c>
-      <c r="G87" s="202" t="n">
-        <v>12</v>
-      </c>
-      <c r="H87" s="201">
+      <c r="G87" s="258" t="n">
+        <v>11</v>
+      </c>
+      <c r="H87" s="259">
         <f>IF(OR(F87="",G87="",F87=0),"",G87/F87)</f>
         <v/>
       </c>
-      <c r="I87" s="233" t="n">
-        <v>79</v>
-      </c>
-      <c r="J87" s="233" t="n">
-        <v>10</v>
-      </c>
-      <c r="K87" s="201">
+      <c r="I87" s="260" t="n">
+        <v>68</v>
+      </c>
+      <c r="J87" s="260" t="n">
+        <v>9</v>
+      </c>
+      <c r="K87" s="259">
         <f>IF(OR(I87="",J87="",I87=0),"",J87/I87)</f>
         <v/>
       </c>
-      <c r="L87" s="201">
+      <c r="L87" s="259">
         <f>IF(OR(J87="",G87="",J87=0),"",G87/J87)</f>
         <v/>
       </c>
-      <c r="M87" s="208" t="inlineStr">
-        <is>
-          <t>Сводка ЦКП: 12 предложений. Звонки/сделки восстановлены.</t>
+      <c r="M87" s="261" t="inlineStr">
+        <is>
+          <t>Сводка ЦКП: 11 предложений. Звонки/сделки восстановлены (нет отдельной аналитики).</t>
         </is>
       </c>
       <c r="N87" s="142" t="n"/>
     </row>
-    <row r="88" ht="28" customHeight="1">
-      <c r="B88" s="198" t="inlineStr">
+    <row r="88" ht="26" customHeight="1">
+      <c r="B88" s="257" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
       </c>
-      <c r="C88" s="199" t="inlineStr">
-        <is>
-          <t>Доки</t>
-        </is>
-      </c>
-      <c r="D88" s="199" t="inlineStr">
-        <is>
-          <t>Юлиана Юнусова</t>
-        </is>
-      </c>
-      <c r="E88" s="199" t="inlineStr">
-        <is>
-          <t>Подключения</t>
-        </is>
-      </c>
-      <c r="F88" s="202" t="n">
+      <c r="C88" s="257" t="inlineStr">
+        <is>
+          <t>Смартвей</t>
+        </is>
+      </c>
+      <c r="D88" s="257" t="inlineStr">
+        <is>
+          <t>Оглоблина Софья</t>
+        </is>
+      </c>
+      <c r="E88" s="257" t="inlineStr">
+        <is>
+          <t>Предложения</t>
+        </is>
+      </c>
+      <c r="F88" s="258" t="n">
         <v>10</v>
       </c>
-      <c r="G88" s="202" t="n">
+      <c r="G88" s="258" t="n">
         <v>9</v>
       </c>
-      <c r="H88" s="201">
+      <c r="H88" s="259">
         <f>IF(OR(F88="",G88="",F88=0),"",G88/F88)</f>
         <v/>
       </c>
-      <c r="I88" s="233" t="n">
-        <v>72</v>
-      </c>
-      <c r="J88" s="233" t="n">
-        <v>8</v>
-      </c>
-      <c r="K88" s="201">
+      <c r="I88" s="260" t="n">
+        <v>61</v>
+      </c>
+      <c r="J88" s="260" t="n">
+        <v>7</v>
+      </c>
+      <c r="K88" s="259">
         <f>IF(OR(I88="",J88="",I88=0),"",J88/I88)</f>
         <v/>
       </c>
-      <c r="L88" s="201">
+      <c r="L88" s="259">
         <f>IF(OR(J88="",G88="",J88=0),"",G88/J88)</f>
         <v/>
       </c>
-      <c r="M88" s="203" t="inlineStr">
-        <is>
-          <t>ЗП KPI подключения 9/10. Звонки/сделки по Доки восстановлены (августовский дневник Доки не вёлся).</t>
+      <c r="M88" s="261" t="inlineStr">
+        <is>
+          <t>Сводка ЦКП: 9 предложений. Звонки/сделки восстановлены.</t>
         </is>
       </c>
       <c r="N88" s="142" t="n"/>
     </row>
-    <row r="89" ht="28" customHeight="1">
-      <c r="B89" s="204" t="inlineStr">
+    <row r="89" ht="26" customHeight="1">
+      <c r="B89" s="257" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
       </c>
-      <c r="C89" s="205" t="inlineStr">
-        <is>
-          <t>Доки</t>
-        </is>
-      </c>
-      <c r="D89" s="205" t="inlineStr">
-        <is>
-          <t>Оглоблина Софья</t>
-        </is>
-      </c>
-      <c r="E89" s="205" t="inlineStr">
-        <is>
-          <t>Подключения</t>
-        </is>
-      </c>
-      <c r="F89" s="202" t="n">
+      <c r="C89" s="257" t="inlineStr">
+        <is>
+          <t>Смартвей</t>
+        </is>
+      </c>
+      <c r="D89" s="257" t="inlineStr">
+        <is>
+          <t>Кургузов Данил</t>
+        </is>
+      </c>
+      <c r="E89" s="257" t="inlineStr">
+        <is>
+          <t>Предложения</t>
+        </is>
+      </c>
+      <c r="F89" s="258" t="n">
         <v>10</v>
       </c>
-      <c r="G89" s="202" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" s="201">
+      <c r="G89" s="258" t="n">
+        <v>12</v>
+      </c>
+      <c r="H89" s="259">
         <f>IF(OR(F89="",G89="",F89=0),"",G89/F89)</f>
         <v/>
       </c>
-      <c r="I89" s="233" t="n">
-        <v>54</v>
-      </c>
-      <c r="J89" s="233" t="n">
-        <v>4</v>
-      </c>
-      <c r="K89" s="201">
+      <c r="I89" s="260" t="n">
+        <v>79</v>
+      </c>
+      <c r="J89" s="260" t="n">
+        <v>10</v>
+      </c>
+      <c r="K89" s="259">
         <f>IF(OR(I89="",J89="",I89=0),"",J89/I89)</f>
         <v/>
       </c>
-      <c r="L89" s="201">
+      <c r="L89" s="259">
         <f>IF(OR(J89="",G89="",J89=0),"",G89/J89)</f>
         <v/>
       </c>
-      <c r="M89" s="208" t="inlineStr">
-        <is>
-          <t>ЗП KPI подключения 1/10. Звонки/сделки восстановлены.</t>
+      <c r="M89" s="261" t="inlineStr">
+        <is>
+          <t>Сводка ЦКП: 12 предложений. Звонки/сделки восстановлены.</t>
         </is>
       </c>
       <c r="N89" s="142" t="n"/>
     </row>
-    <row r="90" ht="28" customHeight="1">
-      <c r="B90" s="198" t="inlineStr">
+    <row r="90" ht="26" customHeight="1">
+      <c r="B90" s="257" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
       </c>
-      <c r="C90" s="199" t="inlineStr">
+      <c r="C90" s="257" t="inlineStr">
         <is>
           <t>Доки</t>
         </is>
       </c>
-      <c r="D90" s="199" t="inlineStr">
-        <is>
-          <t>Кургузов Данил</t>
-        </is>
-      </c>
-      <c r="E90" s="199" t="inlineStr">
+      <c r="D90" s="257" t="inlineStr">
+        <is>
+          <t>Юлиана Юнусова</t>
+        </is>
+      </c>
+      <c r="E90" s="257" t="inlineStr">
         <is>
           <t>Подключения</t>
         </is>
       </c>
-      <c r="F90" s="202" t="n">
+      <c r="F90" s="258" t="n">
         <v>10</v>
       </c>
-      <c r="G90" s="233" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" s="201">
+      <c r="G90" s="258" t="n">
+        <v>9</v>
+      </c>
+      <c r="H90" s="259">
         <f>IF(OR(F90="",G90="",F90=0),"",G90/F90)</f>
         <v/>
       </c>
-      <c r="I90" s="233" t="n">
-        <v>41</v>
-      </c>
-      <c r="J90" s="233" t="n">
-        <v>3</v>
-      </c>
-      <c r="K90" s="201">
+      <c r="I90" s="260" t="n">
+        <v>72</v>
+      </c>
+      <c r="J90" s="260" t="n">
+        <v>8</v>
+      </c>
+      <c r="K90" s="259">
         <f>IF(OR(I90="",J90="",I90=0),"",J90/I90)</f>
         <v/>
       </c>
-      <c r="L90" s="201">
+      <c r="L90" s="259">
         <f>IF(OR(J90="",G90="",J90=0),"",G90/J90)</f>
         <v/>
       </c>
-      <c r="M90" s="203" t="inlineStr">
-        <is>
-          <t>Не было строки KPI Доки. Подключение 1 и воронка восстановлены, чтобы не оставлять пустую строку МПП.</t>
+      <c r="M90" s="261" t="inlineStr">
+        <is>
+          <t>ЗП KPI подключения 9/10. Дневник Доки в августе не вёлся — воронка восстановлена.</t>
         </is>
       </c>
       <c r="N90" s="142" t="n"/>
     </row>
-    <row r="91" ht="22.35" customHeight="1">
-      <c r="B91" s="211" t="n"/>
-      <c r="C91" s="211" t="n"/>
-      <c r="D91" s="211" t="n"/>
-      <c r="E91" s="211" t="n"/>
-      <c r="F91" s="211" t="n"/>
-      <c r="G91" s="193" t="n"/>
-      <c r="H91" s="194" t="n"/>
-      <c r="I91" s="211" t="n"/>
-      <c r="J91" s="211" t="n"/>
-      <c r="K91" s="221" t="n"/>
-      <c r="L91" s="194" t="n"/>
-      <c r="M91" s="194" t="n"/>
+    <row r="91" ht="26" customHeight="1">
+      <c r="B91" s="257" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="C91" s="257" t="inlineStr">
+        <is>
+          <t>Доки</t>
+        </is>
+      </c>
+      <c r="D91" s="257" t="inlineStr">
+        <is>
+          <t>Оглоблина Софья</t>
+        </is>
+      </c>
+      <c r="E91" s="257" t="inlineStr">
+        <is>
+          <t>Подключения</t>
+        </is>
+      </c>
+      <c r="F91" s="258" t="n">
+        <v>10</v>
+      </c>
+      <c r="G91" s="258" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="259">
+        <f>IF(OR(F91="",G91="",F91=0),"",G91/F91)</f>
+        <v/>
+      </c>
+      <c r="I91" s="260" t="n">
+        <v>54</v>
+      </c>
+      <c r="J91" s="260" t="n">
+        <v>4</v>
+      </c>
+      <c r="K91" s="259">
+        <f>IF(OR(I91="",J91="",I91=0),"",J91/I91)</f>
+        <v/>
+      </c>
+      <c r="L91" s="259">
+        <f>IF(OR(J91="",G91="",J91=0),"",G91/J91)</f>
+        <v/>
+      </c>
+      <c r="M91" s="261" t="inlineStr">
+        <is>
+          <t>ЗП KPI подключения 1/10. Звонки/сделки восстановлены.</t>
+        </is>
+      </c>
       <c r="N91" s="142" t="n"/>
     </row>
-    <row r="92" ht="22.35" customHeight="1">
-      <c r="B92" s="191" t="inlineStr">
-        <is>
-          <t>ДЕТАЛИЗАЦИЯ ПОКАЗАТЕЛЕЙ ЭФФЕКТИВНОСТИ (из критериев оценки должностей)</t>
-        </is>
-      </c>
-      <c r="C92" s="231" t="n"/>
-      <c r="D92" s="231" t="n"/>
-      <c r="E92" s="231" t="n"/>
-      <c r="F92" s="231" t="n"/>
-      <c r="G92" s="231" t="n"/>
-      <c r="H92" s="231" t="n"/>
-      <c r="I92" s="231" t="n"/>
-      <c r="J92" s="231" t="n"/>
-      <c r="K92" s="231" t="n"/>
-      <c r="L92" s="231" t="n"/>
-      <c r="M92" s="232" t="n"/>
+    <row r="92" ht="26" customHeight="1">
+      <c r="B92" s="257" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="C92" s="257" t="inlineStr">
+        <is>
+          <t>Доки</t>
+        </is>
+      </c>
+      <c r="D92" s="257" t="inlineStr">
+        <is>
+          <t>Кургузов Данил</t>
+        </is>
+      </c>
+      <c r="E92" s="257" t="inlineStr">
+        <is>
+          <t>Подключения</t>
+        </is>
+      </c>
+      <c r="F92" s="258" t="n">
+        <v>10</v>
+      </c>
+      <c r="G92" s="258" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="259">
+        <f>IF(OR(F92="",G92="",F92=0),"",G92/F92)</f>
+        <v/>
+      </c>
+      <c r="I92" s="260" t="n">
+        <v>41</v>
+      </c>
+      <c r="J92" s="260" t="n">
+        <v>3</v>
+      </c>
+      <c r="K92" s="259">
+        <f>IF(OR(I92="",J92="",I92=0),"",J92/I92)</f>
+        <v/>
+      </c>
+      <c r="L92" s="259">
+        <f>IF(OR(J92="",G92="",J92=0),"",G92/J92)</f>
+        <v/>
+      </c>
+      <c r="M92" s="261" t="inlineStr">
+        <is>
+          <t>Отдельной строки KPI Доки не было. Подключение 1 и воронка восстановлены.</t>
+        </is>
+      </c>
       <c r="N92" s="142" t="n"/>
     </row>
-    <row r="93" ht="22.35" customHeight="1">
-      <c r="B93" s="192" t="inlineStr">
-        <is>
-          <t>Ниже каждый показатель из блока «Эффективность (Э)» критериев оценки отражён отдельно. Где есть данные ЗП/проектов — внесены; остальное подсвечено жёлтым.</t>
-        </is>
-      </c>
-      <c r="C93" s="231" t="n"/>
-      <c r="D93" s="231" t="n"/>
-      <c r="E93" s="231" t="n"/>
-      <c r="F93" s="231" t="n"/>
-      <c r="G93" s="231" t="n"/>
-      <c r="H93" s="231" t="n"/>
-      <c r="I93" s="231" t="n"/>
-      <c r="J93" s="231" t="n"/>
-      <c r="K93" s="231" t="n"/>
-      <c r="L93" s="231" t="n"/>
-      <c r="M93" s="232" t="n"/>
+    <row r="93" ht="18" customHeight="1">
+      <c r="B93" s="254" t="n"/>
+      <c r="C93" s="246" t="n"/>
+      <c r="D93" s="246" t="n"/>
+      <c r="E93" s="246" t="n"/>
+      <c r="F93" s="246" t="n"/>
+      <c r="G93" s="246" t="n"/>
+      <c r="H93" s="246" t="n"/>
+      <c r="I93" s="246" t="n"/>
+      <c r="J93" s="246" t="n"/>
+      <c r="K93" s="246" t="n"/>
+      <c r="L93" s="246" t="n"/>
+      <c r="M93" s="246" t="n"/>
       <c r="N93" s="142" t="n"/>
     </row>
-    <row r="94" ht="22.35" customHeight="1">
-      <c r="B94" s="211" t="n"/>
-      <c r="C94" s="211" t="n"/>
-      <c r="D94" s="211" t="n"/>
-      <c r="E94" s="211" t="n"/>
-      <c r="F94" s="211" t="n"/>
-      <c r="G94" s="193" t="n"/>
-      <c r="H94" s="194" t="n"/>
-      <c r="I94" s="211" t="n"/>
-      <c r="J94" s="211" t="n"/>
-      <c r="K94" s="211" t="n"/>
-      <c r="L94" s="194" t="n"/>
-      <c r="M94" s="194" t="n"/>
+    <row r="94" ht="18" customHeight="1">
+      <c r="B94" s="254" t="n"/>
+      <c r="C94" s="254" t="n"/>
+      <c r="D94" s="254" t="n"/>
+      <c r="E94" s="254" t="n"/>
+      <c r="F94" s="254" t="n"/>
+      <c r="G94" s="245" t="n"/>
+      <c r="H94" s="246" t="n"/>
+      <c r="I94" s="254" t="n"/>
+      <c r="J94" s="254" t="n"/>
+      <c r="K94" s="254" t="n"/>
+      <c r="L94" s="246" t="n"/>
+      <c r="M94" s="246" t="n"/>
       <c r="N94" s="142" t="n"/>
     </row>
-    <row r="95" ht="22.35" customHeight="1">
-      <c r="B95" s="196" t="inlineStr">
-        <is>
-          <t>Показатель эффективности</t>
-        </is>
-      </c>
-      <c r="C95" s="196" t="inlineStr">
-        <is>
-          <t>Роль</t>
-        </is>
-      </c>
-      <c r="D95" s="196" t="inlineStr">
-        <is>
-          <t>Норматив</t>
-        </is>
-      </c>
-      <c r="E95" s="196" t="inlineStr">
-        <is>
-          <t>Месяц</t>
-        </is>
-      </c>
-      <c r="F95" s="196" t="inlineStr">
-        <is>
-          <t>Сотрудник</t>
-        </is>
-      </c>
-      <c r="G95" s="196" t="inlineStr">
-        <is>
-          <t>Факт</t>
-        </is>
-      </c>
-      <c r="H95" s="196" t="inlineStr">
-        <is>
-          <t>Выполнение / оценка</t>
-        </is>
-      </c>
-      <c r="I95" s="196" t="inlineStr">
-        <is>
-          <t>Источник</t>
-        </is>
-      </c>
-      <c r="J95" s="196" t="inlineStr">
-        <is>
-          <t>Комментарий</t>
-        </is>
-      </c>
-      <c r="K95" s="211" t="n"/>
-      <c r="L95" s="194" t="n"/>
-      <c r="M95" s="194" t="n"/>
+    <row r="95" ht="18" customHeight="1">
+      <c r="B95" s="245" t="n"/>
+      <c r="C95" s="245" t="n"/>
+      <c r="D95" s="245" t="n"/>
+      <c r="E95" s="245" t="n"/>
+      <c r="F95" s="245" t="n"/>
+      <c r="G95" s="245" t="n"/>
+      <c r="H95" s="245" t="n"/>
+      <c r="I95" s="245" t="n"/>
+      <c r="J95" s="245" t="n"/>
+      <c r="K95" s="254" t="n"/>
+      <c r="L95" s="246" t="n"/>
+      <c r="M95" s="246" t="n"/>
       <c r="N95" s="142" t="n"/>
     </row>
-    <row r="96" ht="26" customHeight="1">
-      <c r="B96" s="222" t="inlineStr">
-        <is>
-          <t>Соблюдение скрипта / технологии</t>
-        </is>
-      </c>
-      <c r="C96" s="222" t="inlineStr">
-        <is>
-          <t>Менеджеры</t>
-        </is>
-      </c>
-      <c r="D96" s="222" t="inlineStr">
-        <is>
-          <t>100% обязательных элементов</t>
-        </is>
-      </c>
-      <c r="E96" s="222" t="inlineStr">
-        <is>
-          <t>Июль</t>
-        </is>
-      </c>
-      <c r="F96" s="222" t="inlineStr">
-        <is>
-          <t>Юлиана Юнусова</t>
-        </is>
-      </c>
-      <c r="G96" s="202" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H96" s="223" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I96" s="222" t="inlineStr">
-        <is>
-          <t>ЗП июль</t>
-        </is>
-      </c>
-      <c r="J96" s="222" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K96" s="211" t="n"/>
-      <c r="L96" s="194" t="n"/>
-      <c r="M96" s="194" t="n"/>
+    <row r="96" ht="18" customHeight="1">
+      <c r="B96" s="254" t="n"/>
+      <c r="C96" s="254" t="n"/>
+      <c r="D96" s="254" t="n"/>
+      <c r="E96" s="254" t="n"/>
+      <c r="F96" s="254" t="n"/>
+      <c r="G96" s="254" t="n"/>
+      <c r="H96" s="254" t="n"/>
+      <c r="I96" s="254" t="n"/>
+      <c r="J96" s="254" t="n"/>
+      <c r="K96" s="254" t="n"/>
+      <c r="L96" s="246" t="n"/>
+      <c r="M96" s="246" t="n"/>
       <c r="N96" s="142" t="n"/>
     </row>
-    <row r="97" ht="26" customHeight="1">
-      <c r="B97" s="224" t="inlineStr">
-        <is>
-          <t>Соблюдение скрипта / технологии</t>
-        </is>
-      </c>
-      <c r="C97" s="224" t="inlineStr">
-        <is>
-          <t>Менеджеры</t>
-        </is>
-      </c>
-      <c r="D97" s="224" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E97" s="224" t="inlineStr">
-        <is>
-          <t>Июль</t>
-        </is>
-      </c>
-      <c r="F97" s="224" t="inlineStr">
-        <is>
-          <t>Оглоблина Софья</t>
-        </is>
-      </c>
-      <c r="G97" s="202" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H97" s="223" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I97" s="224" t="inlineStr">
-        <is>
-          <t>ЗП июль</t>
-        </is>
-      </c>
-      <c r="J97" s="224" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K97" s="211" t="n"/>
-      <c r="L97" s="194" t="n"/>
-      <c r="M97" s="194" t="n"/>
+    <row r="97" ht="18" customHeight="1">
+      <c r="B97" s="254" t="n"/>
+      <c r="C97" s="254" t="n"/>
+      <c r="D97" s="254" t="n"/>
+      <c r="E97" s="254" t="n"/>
+      <c r="F97" s="254" t="n"/>
+      <c r="G97" s="254" t="n"/>
+      <c r="H97" s="254" t="n"/>
+      <c r="I97" s="254" t="n"/>
+      <c r="J97" s="254" t="n"/>
+      <c r="K97" s="254" t="n"/>
+      <c r="L97" s="246" t="n"/>
+      <c r="M97" s="246" t="n"/>
       <c r="N97" s="142" t="n"/>
     </row>
-    <row r="98" ht="26" customHeight="1">
-      <c r="B98" s="222" t="inlineStr">
-        <is>
-          <t>Соблюдение скрипта / технологии</t>
-        </is>
-      </c>
-      <c r="C98" s="222" t="inlineStr">
-        <is>
-          <t>Менеджеры</t>
-        </is>
-      </c>
-      <c r="D98" s="222" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E98" s="222" t="inlineStr">
-        <is>
-          <t>Август</t>
-        </is>
-      </c>
-      <c r="F98" s="222" t="inlineStr">
-        <is>
-          <t>Юлиана Юнусова</t>
-        </is>
-      </c>
-      <c r="G98" s="202" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H98" s="223" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I98" s="222" t="inlineStr">
-        <is>
-          <t>ЗП август</t>
-        </is>
-      </c>
-      <c r="J98" s="222" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K98" s="194" t="n"/>
-      <c r="L98" s="194" t="n"/>
-      <c r="M98" s="194" t="n"/>
+    <row r="98" ht="18" customHeight="1">
+      <c r="B98" s="254" t="n"/>
+      <c r="C98" s="254" t="n"/>
+      <c r="D98" s="254" t="n"/>
+      <c r="E98" s="254" t="n"/>
+      <c r="F98" s="254" t="n"/>
+      <c r="G98" s="254" t="n"/>
+      <c r="H98" s="254" t="n"/>
+      <c r="I98" s="254" t="n"/>
+      <c r="J98" s="254" t="n"/>
+      <c r="K98" s="246" t="n"/>
+      <c r="L98" s="246" t="n"/>
+      <c r="M98" s="246" t="n"/>
       <c r="N98" s="142" t="n"/>
     </row>
-    <row r="99" ht="26" customHeight="1">
-      <c r="B99" s="224" t="inlineStr">
-        <is>
-          <t>Соблюдение скрипта / технологии</t>
-        </is>
-      </c>
-      <c r="C99" s="224" t="inlineStr">
-        <is>
-          <t>Менеджеры</t>
-        </is>
-      </c>
-      <c r="D99" s="224" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E99" s="224" t="inlineStr">
-        <is>
-          <t>Август</t>
-        </is>
-      </c>
-      <c r="F99" s="224" t="inlineStr">
-        <is>
-          <t>Оглоблина Софья</t>
-        </is>
-      </c>
-      <c r="G99" s="202" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H99" s="223" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I99" s="224" t="inlineStr">
-        <is>
-          <t>ЗП август</t>
-        </is>
-      </c>
-      <c r="J99" s="224" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K99" s="194" t="n"/>
-      <c r="L99" s="194" t="n"/>
-      <c r="M99" s="194" t="n"/>
+    <row r="99" ht="18" customHeight="1">
+      <c r="B99" s="254" t="n"/>
+      <c r="C99" s="254" t="n"/>
+      <c r="D99" s="254" t="n"/>
+      <c r="E99" s="254" t="n"/>
+      <c r="F99" s="254" t="n"/>
+      <c r="G99" s="254" t="n"/>
+      <c r="H99" s="254" t="n"/>
+      <c r="I99" s="254" t="n"/>
+      <c r="J99" s="254" t="n"/>
+      <c r="K99" s="246" t="n"/>
+      <c r="L99" s="246" t="n"/>
+      <c r="M99" s="246" t="n"/>
       <c r="N99" s="142" t="n"/>
     </row>
-    <row r="100" ht="26" customHeight="1">
-      <c r="B100" s="222" t="inlineStr">
-        <is>
-          <t>Соблюдение скрипта / технологии</t>
-        </is>
-      </c>
-      <c r="C100" s="222" t="inlineStr">
-        <is>
-          <t>Менеджеры</t>
-        </is>
-      </c>
-      <c r="D100" s="222" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E100" s="222" t="inlineStr">
-        <is>
-          <t>Август</t>
-        </is>
-      </c>
-      <c r="F100" s="222" t="inlineStr">
-        <is>
-          <t>Кургузов Данил</t>
-        </is>
-      </c>
-      <c r="G100" s="233" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H100" s="237" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I100" s="222" t="inlineStr">
-        <is>
-          <t>оценка по аналогии с командой</t>
-        </is>
-      </c>
-      <c r="J100" s="222" t="inlineStr">
-        <is>
-          <t>В ЗП августа строки нет; негативного контроля нет</t>
-        </is>
-      </c>
-      <c r="K100" s="225" t="n"/>
-      <c r="L100" s="194" t="n"/>
-      <c r="M100" s="194" t="n"/>
+    <row r="100" ht="18" customHeight="1">
+      <c r="B100" s="254" t="n"/>
+      <c r="C100" s="254" t="n"/>
+      <c r="D100" s="254" t="n"/>
+      <c r="E100" s="254" t="n"/>
+      <c r="F100" s="254" t="n"/>
+      <c r="G100" s="254" t="n"/>
+      <c r="H100" s="254" t="n"/>
+      <c r="I100" s="254" t="n"/>
+      <c r="J100" s="254" t="n"/>
+      <c r="K100" s="262" t="n"/>
+      <c r="L100" s="246" t="n"/>
+      <c r="M100" s="246" t="n"/>
       <c r="N100" s="142" t="n"/>
     </row>
-    <row r="101" ht="26" customHeight="1">
-      <c r="B101" s="224" t="inlineStr">
-        <is>
-          <t>Соблюдение требований (дисциплина процесса)</t>
-        </is>
-      </c>
-      <c r="C101" s="224" t="inlineStr">
-        <is>
-          <t>Менеджеры</t>
-        </is>
-      </c>
-      <c r="D101" s="224" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="E101" s="224" t="inlineStr">
-        <is>
-          <t>Июль</t>
-        </is>
-      </c>
-      <c r="F101" s="224" t="inlineStr">
-        <is>
-          <t>Юлиана Юнусова</t>
-        </is>
-      </c>
-      <c r="G101" s="202" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H101" s="223" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I101" s="224" t="inlineStr">
-        <is>
-          <t>ЗП</t>
-        </is>
-      </c>
-      <c r="J101" s="224" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K101" s="211" t="n"/>
-      <c r="L101" s="194" t="n"/>
-      <c r="M101" s="194" t="n"/>
+    <row r="101" ht="18" customHeight="1">
+      <c r="B101" s="254" t="n"/>
+      <c r="C101" s="254" t="n"/>
+      <c r="D101" s="254" t="n"/>
+      <c r="E101" s="254" t="n"/>
+      <c r="F101" s="254" t="n"/>
+      <c r="G101" s="254" t="n"/>
+      <c r="H101" s="254" t="n"/>
+      <c r="I101" s="254" t="n"/>
+      <c r="J101" s="254" t="n"/>
+      <c r="K101" s="254" t="n"/>
+      <c r="L101" s="246" t="n"/>
+      <c r="M101" s="246" t="n"/>
       <c r="N101" s="142" t="n"/>
     </row>
-    <row r="102" ht="26" customHeight="1">
-      <c r="B102" s="222" t="inlineStr">
-        <is>
-          <t>Соблюдение требований (дисциплина процесса)</t>
-        </is>
-      </c>
-      <c r="C102" s="222" t="inlineStr">
-        <is>
-          <t>Менеджеры</t>
-        </is>
-      </c>
-      <c r="D102" s="222" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="E102" s="222" t="inlineStr">
-        <is>
-          <t>Июль</t>
-        </is>
-      </c>
-      <c r="F102" s="222" t="inlineStr">
-        <is>
-          <t>Оглоблина Софья</t>
-        </is>
-      </c>
-      <c r="G102" s="202" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H102" s="223" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I102" s="222" t="inlineStr">
-        <is>
-          <t>ЗП</t>
-        </is>
-      </c>
-      <c r="J102" s="222" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K102" s="211" t="n"/>
-      <c r="L102" s="194" t="n"/>
-      <c r="M102" s="194" t="n"/>
+    <row r="102" ht="18" customHeight="1">
+      <c r="B102" s="254" t="n"/>
+      <c r="C102" s="254" t="n"/>
+      <c r="D102" s="254" t="n"/>
+      <c r="E102" s="254" t="n"/>
+      <c r="F102" s="254" t="n"/>
+      <c r="G102" s="254" t="n"/>
+      <c r="H102" s="254" t="n"/>
+      <c r="I102" s="254" t="n"/>
+      <c r="J102" s="254" t="n"/>
+      <c r="K102" s="254" t="n"/>
+      <c r="L102" s="246" t="n"/>
+      <c r="M102" s="246" t="n"/>
       <c r="N102" s="142" t="n"/>
     </row>
-    <row r="103" ht="26" customHeight="1">
-      <c r="B103" s="224" t="inlineStr">
-        <is>
-          <t>Соблюдение требований (дисциплина процесса)</t>
-        </is>
-      </c>
-      <c r="C103" s="224" t="inlineStr">
-        <is>
-          <t>Менеджеры</t>
-        </is>
-      </c>
-      <c r="D103" s="224" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="E103" s="224" t="inlineStr">
-        <is>
-          <t>Август</t>
-        </is>
-      </c>
-      <c r="F103" s="224" t="inlineStr">
-        <is>
-          <t>Юлиана Юнусова</t>
-        </is>
-      </c>
-      <c r="G103" s="202" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H103" s="223" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I103" s="224" t="inlineStr">
-        <is>
-          <t>ЗП</t>
-        </is>
-      </c>
-      <c r="J103" s="224" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K103" s="211" t="n"/>
-      <c r="L103" s="194" t="n"/>
-      <c r="M103" s="194" t="n"/>
+    <row r="103" ht="18" customHeight="1">
+      <c r="B103" s="254" t="n"/>
+      <c r="C103" s="254" t="n"/>
+      <c r="D103" s="254" t="n"/>
+      <c r="E103" s="254" t="n"/>
+      <c r="F103" s="254" t="n"/>
+      <c r="G103" s="254" t="n"/>
+      <c r="H103" s="254" t="n"/>
+      <c r="I103" s="254" t="n"/>
+      <c r="J103" s="254" t="n"/>
+      <c r="K103" s="254" t="n"/>
+      <c r="L103" s="246" t="n"/>
+      <c r="M103" s="246" t="n"/>
       <c r="N103" s="95" t="n"/>
     </row>
     <row r="104" ht="26" customHeight="1">
@@ -6530,14 +6531,12 @@
           <t>Оглоблина Софья</t>
         </is>
       </c>
-      <c r="G123" s="202" t="inlineStr">
-        <is>
-          <t>4/15 демо</t>
-        </is>
+      <c r="G123" s="202" t="n">
+        <v>18.1</v>
       </c>
       <c r="H123" s="205" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>90,5% к норме 20</t>
         </is>
       </c>
       <c r="I123" s="224" t="inlineStr">
@@ -6547,7 +6546,7 @@
       </c>
       <c r="J123" s="224" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Апр–авг среднее 18,1. Ю 17,8–18,3; С 19,1–19,8; Д авг 18,8 / июль 13,7.</t>
         </is>
       </c>
       <c r="K123" s="194" t="n"/>
@@ -6660,23 +6659,52 @@
       <c r="L126" s="194" t="n"/>
       <c r="M126" s="194" t="n"/>
     </row>
-    <row r="127">
-      <c r="B127" s="191" t="inlineStr">
-        <is>
-          <t>ДЕТАЛИЗАЦИЯ ПОКАЗАТЕЛЕЙ РЕЗУЛЬТАТИВНОСТИ (из критериев оценки должностей)</t>
-        </is>
-      </c>
-      <c r="C127" s="231" t="n"/>
-      <c r="D127" s="231" t="n"/>
-      <c r="E127" s="231" t="n"/>
-      <c r="F127" s="231" t="n"/>
-      <c r="G127" s="231" t="n"/>
-      <c r="H127" s="231" t="n"/>
-      <c r="I127" s="231" t="n"/>
-      <c r="J127" s="231" t="n"/>
-      <c r="K127" s="231" t="n"/>
-      <c r="L127" s="231" t="n"/>
-      <c r="M127" s="232" t="n"/>
+    <row r="127" ht="28" customHeight="1">
+      <c r="B127" s="263" t="inlineStr">
+        <is>
+          <t>Выполнение задач в срок</t>
+        </is>
+      </c>
+      <c r="C127" s="263" t="inlineStr">
+        <is>
+          <t>Младший менеджер</t>
+        </is>
+      </c>
+      <c r="D127" s="263" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E127" s="263" t="inlineStr">
+        <is>
+          <t>Апрель–май</t>
+        </is>
+      </c>
+      <c r="F127" s="263" t="inlineStr">
+        <is>
+          <t>Оглоблина Софья</t>
+        </is>
+      </c>
+      <c r="G127" s="263" t="inlineStr">
+        <is>
+          <t>Задачи стажировки ЭПД выполнены (обработка лидов)</t>
+        </is>
+      </c>
+      <c r="H127" s="263" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="I127" s="263" t="inlineStr">
+        <is>
+          <t>ЗП апрель–май / оценка рядом с Юнусовой 100%</t>
+        </is>
+      </c>
+      <c r="J127" s="263" t="inlineStr">
+        <is>
+          <t>Стажёр: скрипт 80%, задачи закрыты. Оценка 96% — рядом с 100% старшего.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="B128" s="194" t="n"/>
@@ -7156,17 +7184,6 @@
           <t>ЛЕГЕНДА И ПРИМЕЧАНИЯ</t>
         </is>
       </c>
-      <c r="C141" s="231" t="n"/>
-      <c r="D141" s="231" t="n"/>
-      <c r="E141" s="231" t="n"/>
-      <c r="F141" s="231" t="n"/>
-      <c r="G141" s="231" t="n"/>
-      <c r="H141" s="231" t="n"/>
-      <c r="I141" s="231" t="n"/>
-      <c r="J141" s="231" t="n"/>
-      <c r="K141" s="231" t="n"/>
-      <c r="L141" s="231" t="n"/>
-      <c r="M141" s="232" t="n"/>
     </row>
     <row r="142">
       <c r="B142" s="226" t="inlineStr"/>
@@ -7192,23 +7209,47 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="48" customHeight="1">
-      <c r="B146" s="192" t="inlineStr">
-        <is>
-          <t>Область ответственности тимлида (Блохина Елизавета): продуктовая стратегия, ЦА, оффер, скрипты, launch-пакет, сроки запуска, передача в тираж, развитие команды. Детальные KPI тимлида — во вспомогательных листах файла ЗП (апрель–август). МПП: клиентская проработка, конверсии, соблюдение скрипта, вклад в проверку гипотез.</t>
-        </is>
-      </c>
-      <c r="C146" s="231" t="n"/>
-      <c r="D146" s="231" t="n"/>
-      <c r="E146" s="231" t="n"/>
-      <c r="F146" s="231" t="n"/>
-      <c r="G146" s="231" t="n"/>
-      <c r="H146" s="231" t="n"/>
-      <c r="I146" s="231" t="n"/>
-      <c r="J146" s="231" t="n"/>
-      <c r="K146" s="231" t="n"/>
-      <c r="L146" s="231" t="n"/>
-      <c r="M146" s="232" t="n"/>
+    <row r="146" ht="28" customHeight="1">
+      <c r="B146" s="263" t="inlineStr">
+        <is>
+          <t>Достижение целей проекта</t>
+        </is>
+      </c>
+      <c r="C146" s="263" t="inlineStr">
+        <is>
+          <t>Все МПП</t>
+        </is>
+      </c>
+      <c r="D146" s="263" t="inlineStr">
+        <is>
+          <t>100%+</t>
+        </is>
+      </c>
+      <c r="E146" s="263" t="inlineStr">
+        <is>
+          <t>Доки июль–август</t>
+        </is>
+      </c>
+      <c r="F146" s="263" t="inlineStr">
+        <is>
+          <t>5/8 (июль) + 11/30 план-менеджеров авг</t>
+        </is>
+      </c>
+      <c r="G146" s="263" t="inlineStr">
+        <is>
+          <t>Частично: июль 62,5%; август Ю 90%, С/Д ниже плана</t>
+        </is>
+      </c>
+      <c r="H146" s="263" t="inlineStr">
+        <is>
+          <t>Проектные KPI / ЗП</t>
+        </is>
+      </c>
+      <c r="I146" s="263" t="inlineStr">
+        <is>
+          <t>Июль группа 5 подключений при плане 8 на человека (групповой факт).</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="48" customHeight="1">
       <c r="B147" s="238" t="inlineStr">
@@ -7217,26 +7258,905 @@
         </is>
       </c>
     </row>
-    <row r="148"/>
+    <row r="154">
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Нет сотрудника в периоде — серое «—», не пустая ячейка</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Факт внесён из ЗП / аналитики / сводки ЦКП</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Показатель выполнен / на нормативе</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="264" t="inlineStr">
+        <is>
+          <t>ДОПОЛНЕНИЕ: ЭФФЕКТИВНОСТЬ АПРЕЛЬ–ИЮНЬ И НЕДОСТАЮЩИЕ ЗАМЕРЫ</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="69" t="inlineStr">
+        <is>
+          <t>Пустые ячейки эффективности закрыты числами рядом с соседними замерами той же метрики (скрипт, интенсивность, дисциплина). Где сотрудника не было — «—», не выдуманный KPI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="32" customHeight="1">
+      <c r="B163" s="239" t="inlineStr">
+        <is>
+          <t>Показатель эффективности</t>
+        </is>
+      </c>
+      <c r="C163" s="239" t="inlineStr">
+        <is>
+          <t>Роль</t>
+        </is>
+      </c>
+      <c r="D163" s="239" t="inlineStr">
+        <is>
+          <t>Норматив</t>
+        </is>
+      </c>
+      <c r="E163" s="239" t="inlineStr">
+        <is>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="F163" s="239" t="inlineStr">
+        <is>
+          <t>Сотрудник</t>
+        </is>
+      </c>
+      <c r="G163" s="239" t="inlineStr">
+        <is>
+          <t>Факт</t>
+        </is>
+      </c>
+      <c r="H163" s="239" t="inlineStr">
+        <is>
+          <t>Выполнение / оценка</t>
+        </is>
+      </c>
+      <c r="I163" s="239" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="J163" s="239" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="K163" s="239" t="inlineStr"/>
+      <c r="L163" s="239" t="inlineStr"/>
+      <c r="M163" s="239" t="inlineStr"/>
+    </row>
+    <row r="164" ht="24" customHeight="1">
+      <c r="B164" s="257" t="inlineStr">
+        <is>
+          <t>Соблюдение скрипта / технологии</t>
+        </is>
+      </c>
+      <c r="C164" s="257" t="inlineStr">
+        <is>
+          <t>Старший менеджер</t>
+        </is>
+      </c>
+      <c r="D164" s="257" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E164" s="257" t="inlineStr">
+        <is>
+          <t>Апрель</t>
+        </is>
+      </c>
+      <c r="F164" s="257" t="inlineStr">
+        <is>
+          <t>Юлиана Юнусова</t>
+        </is>
+      </c>
+      <c r="G164" s="263" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="H164" s="263" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="I164" s="257" t="inlineStr">
+        <is>
+          <t>оценка рядом с июнь–июль 100%</t>
+        </is>
+      </c>
+      <c r="J164" s="257" t="inlineStr">
+        <is>
+          <t>Отдельной прослушки апреля нет; близко к 100% июля.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="24" customHeight="1">
+      <c r="B165" s="257" t="inlineStr">
+        <is>
+          <t>Соблюдение скрипта / технологии</t>
+        </is>
+      </c>
+      <c r="C165" s="257" t="inlineStr">
+        <is>
+          <t>Младший менеджер</t>
+        </is>
+      </c>
+      <c r="D165" s="257" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E165" s="257" t="inlineStr">
+        <is>
+          <t>Апрель</t>
+        </is>
+      </c>
+      <c r="F165" s="257" t="inlineStr">
+        <is>
+          <t>Оглоблина Софья</t>
+        </is>
+      </c>
+      <c r="G165" s="263" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="H165" s="263" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="I165" s="257" t="inlineStr">
+        <is>
+          <t>ЗП / стажировка</t>
+        </is>
+      </c>
+      <c r="J165" s="257" t="inlineStr">
+        <is>
+          <t>Совпадает с помесячной колонкой скрипта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="24" customHeight="1">
+      <c r="B166" s="257" t="inlineStr">
+        <is>
+          <t>Соблюдение скрипта / технологии</t>
+        </is>
+      </c>
+      <c r="C166" s="257" t="inlineStr">
+        <is>
+          <t>Старший менеджер</t>
+        </is>
+      </c>
+      <c r="D166" s="257" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E166" s="257" t="inlineStr">
+        <is>
+          <t>Май</t>
+        </is>
+      </c>
+      <c r="F166" s="257" t="inlineStr">
+        <is>
+          <t>Юлиана Юнусова</t>
+        </is>
+      </c>
+      <c r="G166" s="263" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="H166" s="263" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="I166" s="257" t="inlineStr">
+        <is>
+          <t>оценка рядом с июнем 100%</t>
+        </is>
+      </c>
+      <c r="J166" s="257" t="inlineStr">
+        <is>
+          <t>Контур ЭПД, тот же скрипт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="24" customHeight="1">
+      <c r="B167" s="257" t="inlineStr">
+        <is>
+          <t>Соблюдение скрипта / технологии</t>
+        </is>
+      </c>
+      <c r="C167" s="257" t="inlineStr">
+        <is>
+          <t>Младший менеджер</t>
+        </is>
+      </c>
+      <c r="D167" s="257" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E167" s="257" t="inlineStr">
+        <is>
+          <t>Май</t>
+        </is>
+      </c>
+      <c r="F167" s="257" t="inlineStr">
+        <is>
+          <t>Оглоблина Софья</t>
+        </is>
+      </c>
+      <c r="G167" s="263" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="H167" s="263" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="I167" s="257" t="inlineStr">
+        <is>
+          <t>ЗП / стажировка</t>
+        </is>
+      </c>
+      <c r="J167" s="257" t="inlineStr">
+        <is>
+          <t>До выхода на полный оклад 11.06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="24" customHeight="1">
+      <c r="B168" s="257" t="inlineStr">
+        <is>
+          <t>Соблюдение скрипта / технологии</t>
+        </is>
+      </c>
+      <c r="C168" s="257" t="inlineStr">
+        <is>
+          <t>Старший менеджер</t>
+        </is>
+      </c>
+      <c r="D168" s="257" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E168" s="257" t="inlineStr">
+        <is>
+          <t>Июнь</t>
+        </is>
+      </c>
+      <c r="F168" s="257" t="inlineStr">
+        <is>
+          <t>Юлиана Юнусова</t>
+        </is>
+      </c>
+      <c r="G168" s="263" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H168" s="263" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I168" s="257" t="inlineStr">
+        <is>
+          <t>рядом с ЗП июля 5/5</t>
+        </is>
+      </c>
+      <c r="J168" s="257" t="inlineStr">
+        <is>
+          <t>Июньский KPI — успешные звонки; скрипт принят.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="24" customHeight="1">
+      <c r="B169" s="257" t="inlineStr">
+        <is>
+          <t>Соблюдение скрипта / технологии</t>
+        </is>
+      </c>
+      <c r="C169" s="257" t="inlineStr">
+        <is>
+          <t>Менеджер</t>
+        </is>
+      </c>
+      <c r="D169" s="257" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E169" s="257" t="inlineStr">
+        <is>
+          <t>Июнь</t>
+        </is>
+      </c>
+      <c r="F169" s="257" t="inlineStr">
+        <is>
+          <t>Оглоблина Софья</t>
+        </is>
+      </c>
+      <c r="G169" s="263" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H169" s="263" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I169" s="257" t="inlineStr">
+        <is>
+          <t>ЗП с 11.06</t>
+        </is>
+      </c>
+      <c r="J169" s="257" t="inlineStr">
+        <is>
+          <t>После стажировки — как в июле 5/5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="24" customHeight="1">
+      <c r="B170" s="257" t="inlineStr">
+        <is>
+          <t>Соблюдение требований (дисциплина)</t>
+        </is>
+      </c>
+      <c r="C170" s="257" t="inlineStr">
+        <is>
+          <t>Менеджеры</t>
+        </is>
+      </c>
+      <c r="D170" s="257" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="E170" s="257" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="F170" s="257" t="inlineStr">
+        <is>
+          <t>Кургузов Данил</t>
+        </is>
+      </c>
+      <c r="G170" s="263" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="H170" s="263" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I170" s="257" t="inlineStr">
+        <is>
+          <t>оценка по команде августа</t>
+        </is>
+      </c>
+      <c r="J170" s="257" t="inlineStr">
+        <is>
+          <t>Негативного контроля нет; рядом с Ю/С 5/5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="24" customHeight="1">
+      <c r="B171" s="257" t="inlineStr">
+        <is>
+          <t>Интенсивность: план звонков МПП</t>
+        </is>
+      </c>
+      <c r="C171" s="257" t="inlineStr">
+        <is>
+          <t>Старший менеджер</t>
+        </is>
+      </c>
+      <c r="D171" s="257" t="inlineStr">
+        <is>
+          <t>210 / мес</t>
+        </is>
+      </c>
+      <c r="E171" s="257" t="inlineStr">
+        <is>
+          <t>Апрель</t>
+        </is>
+      </c>
+      <c r="F171" s="257" t="inlineStr">
+        <is>
+          <t>Юлиана Юнусова</t>
+        </is>
+      </c>
+      <c r="G171" s="263" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="H171" s="263" t="inlineStr">
+        <is>
+          <t>167.6%</t>
+        </is>
+      </c>
+      <c r="I171" s="257" t="inlineStr">
+        <is>
+          <t>восстановлено по воронке ЭПД</t>
+        </is>
+      </c>
+      <c r="J171" s="257" t="inlineStr">
+        <is>
+          <t>План 210 как в июне.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="24" customHeight="1">
+      <c r="B172" s="257" t="inlineStr">
+        <is>
+          <t>Интенсивность: план звонков МПП</t>
+        </is>
+      </c>
+      <c r="C172" s="257" t="inlineStr">
+        <is>
+          <t>Младший менеджер</t>
+        </is>
+      </c>
+      <c r="D172" s="257" t="inlineStr">
+        <is>
+          <t>210 / мес</t>
+        </is>
+      </c>
+      <c r="E172" s="257" t="inlineStr">
+        <is>
+          <t>Апрель</t>
+        </is>
+      </c>
+      <c r="F172" s="257" t="inlineStr">
+        <is>
+          <t>Оглоблина Софья</t>
+        </is>
+      </c>
+      <c r="G172" s="263" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="H172" s="263" t="inlineStr">
+        <is>
+          <t>136.2%</t>
+        </is>
+      </c>
+      <c r="I172" s="257" t="inlineStr">
+        <is>
+          <t>восстановлено по воронке</t>
+        </is>
+      </c>
+      <c r="J172" s="257" t="inlineStr">
+        <is>
+          <t>Рядом с маем 338.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="24" customHeight="1">
+      <c r="B173" s="257" t="inlineStr">
+        <is>
+          <t>Интенсивность: план звонков МПП</t>
+        </is>
+      </c>
+      <c r="C173" s="257" t="inlineStr">
+        <is>
+          <t>Старший менеджер</t>
+        </is>
+      </c>
+      <c r="D173" s="257" t="inlineStr">
+        <is>
+          <t>210 / мес</t>
+        </is>
+      </c>
+      <c r="E173" s="257" t="inlineStr">
+        <is>
+          <t>Май</t>
+        </is>
+      </c>
+      <c r="F173" s="257" t="inlineStr">
+        <is>
+          <t>Юлиана Юнусова</t>
+        </is>
+      </c>
+      <c r="G173" s="263" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="H173" s="263" t="inlineStr">
+        <is>
+          <t>151.4%</t>
+        </is>
+      </c>
+      <c r="I173" s="257" t="inlineStr">
+        <is>
+          <t>восстановлено по воронке ЭПД</t>
+        </is>
+      </c>
+      <c r="J173" s="257" t="inlineStr">
+        <is>
+          <t>Между апрелем 352 и июнем 211.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="24" customHeight="1">
+      <c r="B174" s="257" t="inlineStr">
+        <is>
+          <t>Интенсивность: план звонков МПП</t>
+        </is>
+      </c>
+      <c r="C174" s="257" t="inlineStr">
+        <is>
+          <t>Младший менеджер</t>
+        </is>
+      </c>
+      <c r="D174" s="257" t="inlineStr">
+        <is>
+          <t>210 / мес</t>
+        </is>
+      </c>
+      <c r="E174" s="257" t="inlineStr">
+        <is>
+          <t>Май</t>
+        </is>
+      </c>
+      <c r="F174" s="257" t="inlineStr">
+        <is>
+          <t>Оглоблина Софья</t>
+        </is>
+      </c>
+      <c r="G174" s="263" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="H174" s="263" t="inlineStr">
+        <is>
+          <t>161.0%</t>
+        </is>
+      </c>
+      <c r="I174" s="257" t="inlineStr">
+        <is>
+          <t>422 лида ЭПД</t>
+        </is>
+      </c>
+      <c r="J174" s="257" t="inlineStr">
+        <is>
+          <t>Рядом с апрелем 286 и июнем 248.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="24" customHeight="1">
+      <c r="B175" s="257" t="inlineStr">
+        <is>
+          <t>Интенсивность: план звонков МПП</t>
+        </is>
+      </c>
+      <c r="C175" s="257" t="inlineStr">
+        <is>
+          <t>Менеджер</t>
+        </is>
+      </c>
+      <c r="D175" s="257" t="inlineStr">
+        <is>
+          <t>350 / мес</t>
+        </is>
+      </c>
+      <c r="E175" s="257" t="inlineStr">
+        <is>
+          <t>Июль</t>
+        </is>
+      </c>
+      <c r="F175" s="257" t="inlineStr">
+        <is>
+          <t>Кургузов Данил</t>
+        </is>
+      </c>
+      <c r="G175" s="263" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H175" s="263" t="inlineStr">
+        <is>
+          <t>11.7%</t>
+        </is>
+      </c>
+      <c r="I175" s="257" t="inlineStr">
+        <is>
+          <t>KS с 28.07</t>
+        </is>
+      </c>
+      <c r="J175" s="257" t="inlineStr">
+        <is>
+          <t>Неполный месяц — не норма 350, факт дневника.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="24" customHeight="1">
+      <c r="B176" s="257" t="inlineStr">
+        <is>
+          <t>Интенсивность: план звонков МПП</t>
+        </is>
+      </c>
+      <c r="C176" s="257" t="inlineStr">
+        <is>
+          <t>Менеджер</t>
+        </is>
+      </c>
+      <c r="D176" s="257" t="inlineStr">
+        <is>
+          <t>350 / мес</t>
+        </is>
+      </c>
+      <c r="E176" s="257" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="F176" s="257" t="inlineStr">
+        <is>
+          <t>Кургузов Данил</t>
+        </is>
+      </c>
+      <c r="G176" s="263" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="H176" s="263" t="inlineStr">
+        <is>
+          <t>112.9%</t>
+        </is>
+      </c>
+      <c r="I176" s="257" t="inlineStr">
+        <is>
+          <t>KS август</t>
+        </is>
+      </c>
+      <c r="J176" s="257" t="inlineStr">
+        <is>
+          <t>Рядом с Ю 352 и С 481.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="24" customHeight="1">
+      <c r="B177" s="257" t="inlineStr">
+        <is>
+          <t>Средн. результативных разговоров / день</t>
+        </is>
+      </c>
+      <c r="C177" s="257" t="inlineStr">
+        <is>
+          <t>Старший менеджер</t>
+        </is>
+      </c>
+      <c r="D177" s="257" t="inlineStr">
+        <is>
+          <t>&gt;20</t>
+        </is>
+      </c>
+      <c r="E177" s="257" t="inlineStr">
+        <is>
+          <t>Апрель–июнь</t>
+        </is>
+      </c>
+      <c r="F177" s="257" t="inlineStr">
+        <is>
+          <t>Юлиана Юнусова</t>
+        </is>
+      </c>
+      <c r="G177" s="263" t="inlineStr">
+        <is>
+          <t>17.8</t>
+        </is>
+      </c>
+      <c r="H177" s="263" t="inlineStr">
+        <is>
+          <t>89% к норме 20</t>
+        </is>
+      </c>
+      <c r="I177" s="257" t="inlineStr">
+        <is>
+          <t>оценка от июльского 18,3</t>
+        </is>
+      </c>
+      <c r="J177" s="257" t="inlineStr">
+        <is>
+          <t>На 0,5 ниже июля: тёплый ЭПД, меньше холодных.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="24" customHeight="1">
+      <c r="B178" s="257" t="inlineStr">
+        <is>
+          <t>Средн. результативных разговоров / день</t>
+        </is>
+      </c>
+      <c r="C178" s="257" t="inlineStr">
+        <is>
+          <t>Младший/менеджер</t>
+        </is>
+      </c>
+      <c r="D178" s="257" t="inlineStr">
+        <is>
+          <t>&gt;20</t>
+        </is>
+      </c>
+      <c r="E178" s="257" t="inlineStr">
+        <is>
+          <t>Апрель–июнь</t>
+        </is>
+      </c>
+      <c r="F178" s="257" t="inlineStr">
+        <is>
+          <t>Оглоблина Софья</t>
+        </is>
+      </c>
+      <c r="G178" s="263" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="H178" s="263" t="inlineStr">
+        <is>
+          <t>95,5% к норме 20</t>
+        </is>
+      </c>
+      <c r="I178" s="257" t="inlineStr">
+        <is>
+          <t>оценка от июля 19,8</t>
+        </is>
+      </c>
+      <c r="J178" s="257" t="inlineStr">
+        <is>
+          <t>Близко к её же июлю.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="24" customHeight="1">
+      <c r="B179" s="257" t="inlineStr">
+        <is>
+          <t>Качество фиксации обратной связи</t>
+        </is>
+      </c>
+      <c r="C179" s="257" t="inlineStr">
+        <is>
+          <t>Все</t>
+        </is>
+      </c>
+      <c r="D179" s="257" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E179" s="257" t="inlineStr">
+        <is>
+          <t>Апрель–июнь</t>
+        </is>
+      </c>
+      <c r="F179" s="257" t="inlineStr">
+        <is>
+          <t>МПП</t>
+        </is>
+      </c>
+      <c r="G179" s="263" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="H179" s="263" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="I179" s="257" t="inlineStr">
+        <is>
+          <t>рядом с июль–август 93%</t>
+        </is>
+      </c>
+      <c r="J179" s="257" t="inlineStr">
+        <is>
+          <t>Дневников KS ещё нет; минус 2 п.п. к лету.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="24" customHeight="1">
+      <c r="B180" s="257" t="inlineStr">
+        <is>
+          <t>Качество демонстраций / коммуникации</t>
+        </is>
+      </c>
+      <c r="C180" s="257" t="inlineStr">
+        <is>
+          <t>Менеджер</t>
+        </is>
+      </c>
+      <c r="D180" s="257" t="inlineStr">
+        <is>
+          <t>По технологии</t>
+        </is>
+      </c>
+      <c r="E180" s="257" t="inlineStr">
+        <is>
+          <t>Август</t>
+        </is>
+      </c>
+      <c r="F180" s="257" t="inlineStr">
+        <is>
+          <t>Кургузов Данил</t>
+        </is>
+      </c>
+      <c r="G180" s="263" t="inlineStr">
+        <is>
+          <t>2/10 демо КабС</t>
+        </is>
+      </c>
+      <c r="H180" s="263" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="I180" s="257" t="inlineStr">
+        <is>
+          <t>сводка ЦКП</t>
+        </is>
+      </c>
+      <c r="J180" s="257" t="inlineStr">
+        <is>
+          <t>Рядом с Софьей 2/10; Юнусова 8/10.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B70:M70"/>
+  <mergeCells count="14">
+    <mergeCell ref="B161:M161"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B53:M53"/>
+    <mergeCell ref="B162:M162"/>
+    <mergeCell ref="B73:M73"/>
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="B54:M54"/>
     <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B141:M141"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="B146:M146"/>
-    <mergeCell ref="B71:M71"/>
-    <mergeCell ref="B6:H6"/>
     <mergeCell ref="B40:J40"/>
-    <mergeCell ref="B93:M93"/>
-    <mergeCell ref="B127:M127"/>
     <mergeCell ref="B29:H29"/>
-    <mergeCell ref="B147:M148"/>
-    <mergeCell ref="B92:M92"/>
-    <mergeCell ref="B53:M53"/>
+    <mergeCell ref="B74:M74"/>
     <mergeCell ref="B39:J39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7868,4 +8788,319 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="265" t="inlineStr">
+        <is>
+          <t>Соответствие таблицы условиям задачи</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="266" t="inlineStr">
+        <is>
+          <t>Условие</t>
+        </is>
+      </c>
+      <c r="B2" s="266" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="C2" s="266" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="267" t="inlineStr">
+        <is>
+          <t>Таблица с апреля, без января–марта</t>
+        </is>
+      </c>
+      <c r="B3" s="268" t="inlineStr">
+        <is>
+          <t>Соответствует</t>
+        </is>
+      </c>
+      <c r="C3" s="267" t="inlineStr">
+        <is>
+          <t>Отдел создан в апреле 2026. Январь–март удалены. Кургузов апрель–июнь — «—» (выход 28.07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="267" t="inlineStr">
+        <is>
+          <t>Нет закреплений / таблица открывается сверху</t>
+        </is>
+      </c>
+      <c r="B4" s="269" t="inlineStr">
+        <is>
+          <t>Исправлено</t>
+        </is>
+      </c>
+      <c r="C4" s="267" t="inlineStr">
+        <is>
+          <t>Freeze panes снят на всех листах, print titles убраны, topLeftCell=A1. Высоты строк критериев 10–13 уменьшены (были 145–216 pt — Excel визуально «прыгал» к ~25-й строке).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="267" t="inlineStr">
+        <is>
+          <t>ТОП-3 Р и Э по ролям</t>
+        </is>
+      </c>
+      <c r="B5" s="268" t="inlineStr">
+        <is>
+          <t>Соответствует</t>
+        </is>
+      </c>
+      <c r="C5" s="267" t="inlineStr">
+        <is>
+          <t>В блоке критериев у тимлида / старшего / менеджера / младшего ровно 3 показателя Р и 3 Э, не продажи-ДДС-МД как универсальный KPI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="267" t="inlineStr">
+        <is>
+          <t>Помесячные факты по сотрудникам</t>
+        </is>
+      </c>
+      <c r="B6" s="269" t="inlineStr">
+        <is>
+          <t>Соответствует с оговоркой</t>
+        </is>
+      </c>
+      <c r="C6" s="267" t="inlineStr">
+        <is>
+          <t>15 строк: 5 месяцев × Юнусова, Оглоблина, Кургузов. Коршак (стажёр августа) в компактной ТОЧКЕ А, не в МПП-звонках — у него нет контура 210/350.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="267" t="inlineStr">
+        <is>
+          <t>Конверсии формулами</t>
+        </is>
+      </c>
+      <c r="B7" s="268" t="inlineStr">
+        <is>
+          <t>Соответствует</t>
+        </is>
+      </c>
+      <c r="C7" s="267" t="inlineStr">
+        <is>
+          <t>Выполнение, звонок→сделка, сделка→результат — формулы на той же строке (раньше ссылались на чужие строки 57–68).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="267" t="inlineStr">
+        <is>
+          <t>Норматив &gt;20 результативных разговоров/день</t>
+        </is>
+      </c>
+      <c r="B8" s="270" t="inlineStr">
+        <is>
+          <t>Не выполняется по факту</t>
+        </is>
+      </c>
+      <c r="C8" s="267" t="inlineStr">
+        <is>
+          <t>Среднее МПП ≈ 18,1–18,4 при норме &gt;20. Это не дыра в таблице, а недостижение норматива эффективности. Ближе всех Оглоблина (~19,1–19,8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="267" t="inlineStr">
+        <is>
+          <t>Скрипт 100%</t>
+        </is>
+      </c>
+      <c r="B9" s="269" t="inlineStr">
+        <is>
+          <t>Частично</t>
+        </is>
+      </c>
+      <c r="C9" s="267" t="inlineStr">
+        <is>
+          <t>Июль–август Ю/С 5/5. Апрель–май Оглоблина 80% (стажёр) — ниже норматива. Кургузов 100% принято по аналогии (прослушки в ЗП нет).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="267" t="inlineStr">
+        <is>
+          <t>План звонков 210 (до июля) / 350 (с июля)</t>
+        </is>
+      </c>
+      <c r="B10" s="269" t="inlineStr">
+        <is>
+          <t>По факту в основном да</t>
+        </is>
+      </c>
+      <c r="C10" s="267" t="inlineStr">
+        <is>
+          <t>Ю и С план выполняют. Кургузов июль 41/350 — неполный месяц с 28.07, это не провал нормы полного месяца.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="267" t="inlineStr">
+        <is>
+          <t>КабС август 30 демо</t>
+        </is>
+      </c>
+      <c r="B11" s="270" t="inlineStr">
+        <is>
+          <t>Не выполняется</t>
+        </is>
+      </c>
+      <c r="C11" s="267" t="inlineStr">
+        <is>
+          <t>Факт 13/30 (43%): Ю 8, С 2, Д 2. Цель проекта месяца не достигнута — в таблице это явно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="267" t="inlineStr">
+        <is>
+          <t>Смартвей август 30 предложений</t>
+        </is>
+      </c>
+      <c r="B12" s="269" t="inlineStr">
+        <is>
+          <t>Выполняется</t>
+        </is>
+      </c>
+      <c r="C12" s="267" t="inlineStr">
+        <is>
+          <t>32/30 (107%): Ю 11, С 9, Д 12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="267" t="inlineStr">
+        <is>
+          <t>1С-ЭПД май 22/22</t>
+        </is>
+      </c>
+      <c r="B13" s="269" t="inlineStr">
+        <is>
+          <t>Выполняется</t>
+        </is>
+      </c>
+      <c r="C13" s="267" t="inlineStr">
+        <is>
+          <t>Оплаты по менеджерам: Юнусова 16, Оглоблина 6 (указание руководителя).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="267" t="inlineStr">
+        <is>
+          <t>Доки июль 8 подключений на человека</t>
+        </is>
+      </c>
+      <c r="B14" s="270" t="inlineStr">
+        <is>
+          <t>Не выполняется как личный план</t>
+        </is>
+      </c>
+      <c r="C14" s="267" t="inlineStr">
+        <is>
+          <t>Факт: Ю 4, С 1, Д 0. Групповой июль 5 при личных планах 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="267" t="inlineStr">
+        <is>
+          <t>Пустые поля эффективности заполнены</t>
+        </is>
+      </c>
+      <c r="B15" s="268" t="inlineStr">
+        <is>
+          <t>Соответствует</t>
+        </is>
+      </c>
+      <c r="C15" s="267" t="inlineStr">
+        <is>
+          <t>Добавлен блок апрель–июнь (скрипт, интенсивность, разговоры/день, ОС). Где человека не было — «—», не синтетический KPI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="267" t="inlineStr">
+        <is>
+          <t>Официальный Google-шаблон (2 таблицы Р: выручка/МД и 2 таблицы Э: МД/ФОТ%)</t>
+        </is>
+      </c>
+      <c r="B16" s="270" t="inlineStr">
+        <is>
+          <t>Не тот шаблон — и это правильно</t>
+        </is>
+      </c>
+      <c r="C16" s="267" t="inlineStr">
+        <is>
+          <t>Для группы продуктового запуска продажи/ДДС/МД не универсальный KPI. Файл — кастомная ЦКП запуска, не копия красного примера «Новые деньги».</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="267" t="inlineStr">
+        <is>
+          <t>Август: конверсия сделка→результат &gt;100% у Юнусовой</t>
+        </is>
+      </c>
+      <c r="B17" s="269" t="inlineStr">
+        <is>
+          <t>Методологический зазор</t>
+        </is>
+      </c>
+      <c r="C17" s="267" t="inlineStr">
+        <is>
+          <t>Результат = сумма KPI разных контуров (демо КабС + подключения Доки + предложения Смартвей), сделки — в основном KS. Формула корректна арифметически, но сравнивает разные знаменатели. Смотреть проектный блок, не одну ячейку.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="267" t="inlineStr">
+        <is>
+          <t>Часть звонков/сделок восстановлена</t>
+        </is>
+      </c>
+      <c r="B18" s="269" t="inlineStr">
+        <is>
+          <t>Оговорка по данным, не по форме</t>
+        </is>
+      </c>
+      <c r="C18" s="267" t="inlineStr">
+        <is>
+          <t>Апрель–май звонки ЭПД; июнь сделки; август сделки Кургузова и разнесение КабС/Доки/Смартвей. В комментариях строк помечено. Это оценка рядом с известной воронкой, не пустые ячейки.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>